--- a/LISTA.xlsx
+++ b/LISTA.xlsx
@@ -663,7 +663,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.04</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>

--- a/LISTA.xlsx
+++ b/LISTA.xlsx
@@ -663,11 +663,7 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>V.01 R.04</t>
-        </is>
-      </c>
+      <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -2084,7 +2080,7 @@
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>QA Pile</t>
+          <t>Validating</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">

--- a/LISTA.xlsx
+++ b/LISTA.xlsx
@@ -1624,7 +1624,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>ZendeskTicket</t>
+          <t>V.01 R.05; ZendeskTicket</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>ZendeskTicket</t>
+          <t>V.01 R.05; ZendeskTicket</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -1793,7 +1793,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -1895,7 +1899,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -2080,7 +2088,7 @@
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Validating</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
@@ -2105,7 +2113,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>ZendeskTicket</t>
+          <t>V.01 R.05; ZendeskTicket</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -2156,7 +2164,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -2262,7 +2274,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -2480,7 +2496,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>ZendeskTicket</t>
+          <t>V.01 R.05; ZendeskTicket</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -2590,7 +2606,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>ZendeskTicket</t>
+          <t>V.01 R.05; ZendeskTicket</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -2975,7 +2991,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -3077,7 +3097,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -3187,7 +3211,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -3240,7 +3268,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -3342,7 +3374,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -3448,7 +3484,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -3501,7 +3541,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -4409,7 +4453,7 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>ZendeskTicket</t>
+          <t>V.01 R.05; ZendeskTicket</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -4617,7 +4661,7 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>ZendeskTicket</t>
+          <t>V.01 R.05; ZendeskTicket</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
@@ -5315,7 +5359,7 @@
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Exploratório</t>
+          <t>Exploratório; V.01 R.05</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
@@ -8009,7 +8053,7 @@
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>Exploratório</t>
+          <t>Exploratório; V.01 R.05</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
@@ -31939,7 +31983,7 @@
       <c r="F609" s="2" t="inlineStr"/>
       <c r="G609" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H609" s="2" t="n">
@@ -34677,7 +34721,11 @@
           <t>Feature</t>
         </is>
       </c>
-      <c r="N662" s="2" t="inlineStr"/>
+      <c r="N662" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O662" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -35379,7 +35427,11 @@
           <t>Feature</t>
         </is>
       </c>
-      <c r="N676" s="2" t="inlineStr"/>
+      <c r="N676" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O676" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -35585,7 +35637,7 @@
       </c>
       <c r="N680" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q2; V.01 R.05</t>
         </is>
       </c>
       <c r="O680" s="2" t="inlineStr">
@@ -35740,7 +35792,11 @@
           <t>Feature</t>
         </is>
       </c>
-      <c r="N683" s="2" t="inlineStr"/>
+      <c r="N683" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O683" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -36248,7 +36304,7 @@
       </c>
       <c r="N693" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q2; V.01 R.05</t>
         </is>
       </c>
       <c r="O693" s="2" t="inlineStr">

--- a/LISTA.xlsx
+++ b/LISTA.xlsx
@@ -1228,7 +1228,7 @@
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
@@ -1241,7 +1241,11 @@
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Mauricio Barossi</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -2334,12 +2338,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Promob\Wonder Squad\Plus</t>
+          <t>Promob\Wonder Squad</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q3</t>
         </is>
       </c>
       <c r="Q36" s="2" t="n">
@@ -2401,20 +2405,20 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>156958</v>
+        <v>157092</v>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>** - Wonder - Plus - Modelo - Porta Colonial - Modelo fica desconfigurado</t>
+          <t>* - Wonder - Essential - Puxadores inseridos incorretamente em módulos superiores</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>QA Pile</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
@@ -2422,14 +2426,14 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2083127</t>
+          <t>2086624</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Heloisa Schweizer de Oliveira</t>
+          <t>Mauricio Barossi</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2439,7 +2443,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>ZendeskTicket</t>
+          <t>V.01 R.05; ZendeskTicket</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -2458,37 +2462,33 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>157092</v>
+        <v>157144</v>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>* - Wonder - Essential - Puxadores inseridos incorretamente em módulos superiores</t>
+          <t>** - Wonder - PNP - Professional com Cut Pro - Configurações faltantes</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>QA Pile</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2086624</t>
+          <t>2087578</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>Mauricio Barossi</t>
-        </is>
-      </c>
+      <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>V.01 R.05; ZendeskTicket</t>
+          <t>ZendeskTicket</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -2515,33 +2515,37 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>157144</v>
+        <v>157175</v>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>** - Wonder - PNP - Professional com Cut Pro - Configurações faltantes</t>
+          <t>** - Wonder - Maker Br - Parceiro Rometal - Ao inserir portas ocorre inconformidade</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA Pile</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2087578</t>
+          <t>2087972</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -2549,7 +2553,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>ZendeskTicket</t>
+          <t>V.01 R.05; ZendeskTicket</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -2568,20 +2572,20 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>157175</v>
+        <v>157288</v>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>** - Wonder - Maker Br - Parceiro Rometal - Ao inserir portas ocorre inconformidade</t>
+          <t>** - Wonder - PNP - Professional com Cut Pro - Configurador de dimensões - Configurações de corrediças não disponíveis</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>QA Pile</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
@@ -2589,14 +2593,14 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2087972</t>
+          <t>2089586</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Heloisa Schweizer de Oliveira</t>
+          <t>Gustavo Garbin de Lima</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -2606,7 +2610,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>V.01 R.05; ZendeskTicket</t>
+          <t>ZendeskTicket</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -2625,20 +2629,20 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>157288</v>
+        <v>157344</v>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>** - Wonder - PNP - Professional com Cut Pro - Configurador de dimensões - Configurações de corrediças não disponíveis</t>
+          <t>2090275- Promob Wonder squad - Sem borda frontal exportando do Promob Professional</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
@@ -2646,7 +2650,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2089586</t>
+          <t>2090275</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -2682,28 +2686,28 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>157344</v>
+        <v>157366</v>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2090275- Promob Wonder squad - Sem borda frontal exportando do Promob Professional</t>
+          <t>Promob -  Maker - Orçamento - Configurador de preços trava ao abrir [P2]</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2090275</t>
+          <t>2088579</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -2739,13 +2743,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>157366</v>
+        <v>157396</v>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Promob -  Maker - Orçamento - Configurador de preços trava ao abrir [P2]</t>
+          <t>** - Wonder - Professional - Orçamento - Fita de borda apresentando-se na listagem com valor incorreto</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2756,11 +2760,11 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2088579</t>
+          <t>2067532</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -2796,37 +2800,33 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>157396</v>
+        <v>157453</v>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>** - Wonder - Professional - Orçamento - Fita de borda apresentando-se na listagem com valor incorreto</t>
+          <t>2093577 - Wonder Squad - Maker BR - Composição Laminada no Plano de Corte</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2067532</t>
+          <t>2093577</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>Gustavo Garbin de Lima</t>
-        </is>
-      </c>
+      <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -2853,13 +2853,13 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>157453</v>
+        <v>157554</v>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2093577 - Wonder Squad - Maker BR - Composição Laminada no Plano de Corte</t>
+          <t>2262042 e 2262040  - Erro lado da fita de borda – configurador</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2870,11 +2870,11 @@
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2093577</t>
+          <t>2262042 e 2262040</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -2885,11 +2885,7 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>ZendeskTicket</t>
-        </is>
-      </c>
+      <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -2906,20 +2902,20 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>157554</v>
+        <v>157617</v>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2262042 e 2262040  - Erro lado da fita de borda – configurador</t>
+          <t>2262030 - Todos os cantos L direito estão com erro</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
@@ -2927,18 +2923,26 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2262042 e 2262040</t>
+          <t>2262030</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Guilherme Fernandes da Silva</t>
+        </is>
+      </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="N47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -2955,47 +2959,39 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>157617</v>
+        <v>157618</v>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2262030 - Todos os cantos L direito estão com erro</t>
+          <t>2262031 - Travessa traseira com erro na medida</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2262030</t>
+          <t>2262031</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>Guilherme Fernandes da Silva</t>
-        </is>
-      </c>
+      <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>V.01 R.05</t>
-        </is>
-      </c>
+      <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -3012,39 +3008,47 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>157618</v>
+        <v>157621</v>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2262031 - Travessa traseira com erro na medida</t>
+          <t>2262041 - Erro lado da fita de borda - configurador (canto L)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2262031</t>
+          <t>2262041</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Guilherme Fernandes da Silva</t>
+        </is>
+      </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="N49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -3061,35 +3065,35 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>157621</v>
+        <v>157633</v>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2262041 - Erro lado da fita de borda - configurador (canto L)</t>
+          <t>2262055 - cozinha -  afastador não estão seguindo o configurador</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2262041</t>
+          <t>2262055</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Fernandes da Silva</t>
+          <t>Mauricio Barossi</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -3099,7 +3103,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>V.01 R.05</t>
+          <t>V.01 R.04</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -3118,13 +3122,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>157633</v>
+        <v>157634</v>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2262055 - cozinha -  afastador não estão seguindo o configurador</t>
+          <t>2262062  - Portas cava - ilhas superiores</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -3135,18 +3139,18 @@
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2262055</t>
+          <t>2262062</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Barossi</t>
+          <t>Guilherme Fernandes da Silva</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3156,7 +3160,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>V.01 R.04</t>
+          <t>V.01 R.05</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -3175,20 +3179,20 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>157634</v>
+        <v>157638</v>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>2262062  - Portas cava - ilhas superiores</t>
+          <t>2262068  - Rodapé canto reto com erro</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>QA Pile</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
@@ -3196,7 +3200,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2262062</t>
+          <t>2262068</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -3223,7 +3227,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q3</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q52" s="2" t="n">
@@ -3232,47 +3236,39 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>157638</v>
+        <v>157639</v>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>2262068  - Rodapé canto reto com erro</t>
+          <t>2262072 - Falta atributo para travessa Dormitório</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>QA Pile</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2262068</t>
+          <t>2262072</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>Guilherme Fernandes da Silva</t>
-        </is>
-      </c>
+      <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>V.01 R.05</t>
-        </is>
-      </c>
+      <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -3289,39 +3285,47 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>157639</v>
+        <v>157640</v>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>2262072 - Falta atributo para travessa Dormitório</t>
+          <t>2262073 - Travessa entrando na porta cega</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2262072</t>
+          <t>2262073</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="N54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -3329,7 +3333,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q3</t>
         </is>
       </c>
       <c r="Q54" s="2" t="n">
@@ -3338,20 +3342,20 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>157640</v>
+        <v>157642</v>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>2262073 - Travessa entrando na porta cega</t>
+          <t>2262074, 2262077 e 2262079  - Erro nos roda pé Cantoneiras diagonal</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
@@ -3359,14 +3363,14 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2262073</t>
+          <t xml:space="preserve">2262074, 2262077 e 2262079 </t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Heloisa Schweizer de Oliveira</t>
+          <t>Guilherme Fernandes da Silva</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3374,11 +3378,7 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>V.01 R.05</t>
-        </is>
-      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q3</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q55" s="2" t="n">
@@ -3395,20 +3395,20 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>157642</v>
+        <v>157645</v>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>2262074, 2262077 e 2262079  - Erro nos roda pé Cantoneiras diagonal</t>
+          <t>2262094 - Erro no rodapé do Bau</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>QA Pile</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
@@ -3416,14 +3416,14 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262074, 2262077 e 2262079 </t>
+          <t>2262094</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Fernandes da Silva</t>
+          <t>Heloisa Schweizer de Oliveira</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -3431,7 +3431,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05</t>
+        </is>
+      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -3439,7 +3443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q3</t>
         </is>
       </c>
       <c r="Q56" s="2" t="n">
@@ -3448,28 +3452,28 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>157645</v>
+        <v>157649</v>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>2262094 - Erro no rodapé do Bau</t>
+          <t>2262102 - Painel sem o ripado</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>QA Pile</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2262094</t>
+          <t>2262102</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -3505,13 +3509,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>157649</v>
+        <v>157650</v>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>2262102 - Painel sem o ripado</t>
+          <t>2262114 - Prateleira na posição errada - Báscula Inf/Sup</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -3526,7 +3530,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2262102</t>
+          <t>2262114</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -3543,7 +3547,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>V.01 R.05</t>
+          <t>V.01 R.04</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -3562,47 +3566,35 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>157650</v>
+        <v>157651</v>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>2262114 - Prateleira na posição errada - Báscula Inf/Sup</t>
+          <t>2262152 - Divisórias com altura errada</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>2262114</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>V.01 R.04</t>
-        </is>
-      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -3610,7 +3602,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q3</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q59" s="2" t="n">
@@ -3619,13 +3611,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>157651</v>
+        <v>157661</v>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2262152 - Divisórias com altura errada</t>
+          <t>2262155 - A Altura do trilho está na posição errada em relação a travessa.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -3636,9 +3628,13 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>2262155</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
@@ -3664,13 +3660,13 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>157661</v>
+        <v>157666</v>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>2262155 - A Altura do trilho está na posição errada em relação a travessa.</t>
+          <t>2262246 - Altura de roda pé lateral - deslizante externo</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -3685,7 +3681,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2262155</t>
+          <t>2262246</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -3713,13 +3709,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>157666</v>
+        <v>157677</v>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>2262246 - Altura de roda pé lateral - deslizante externo</t>
+          <t>2262180 - Erro nas prateleiras / armário despenseiro</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -3734,7 +3730,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2262246</t>
+          <t>2262180</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -3762,13 +3758,13 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>157677</v>
+        <v>157679</v>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>2262180 - Erro nas prateleiras / armário despenseiro</t>
+          <t>2262176 - Erro travessa traseira construtor de armários</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -3783,7 +3779,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2262180</t>
+          <t>2262176</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -3811,33 +3807,37 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>157679</v>
+        <v>157687</v>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>2262176 - Erro travessa traseira construtor de armários</t>
+          <t>2256983 - Start V13 R33 - Questões relacionadas ao parceiro Império do Marceneiro</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2262176</t>
+          <t>2256983</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Jessica Suiani dos Santos Babinski</t>
+        </is>
+      </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -3860,37 +3860,33 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>157687</v>
+        <v>157697</v>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>2256983 - Start V13 R33 - Questões relacionadas ao parceiro Império do Marceneiro</t>
+          <t>2262066 - Erros nas prateleiras e fundo - cava madeira</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2256983</t>
+          <t>2262066</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>Jessica Suiani dos Santos Babinski</t>
-        </is>
-      </c>
+      <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -3913,13 +3909,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>157697</v>
+        <v>157720</v>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr"/>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>2262066 - Erros nas prateleiras e fundo - cava madeira</t>
+          <t>2262100 - Erro em praticamente todos os módulos da linha de sala</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -3934,7 +3930,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2262066</t>
+          <t>2262100</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -3962,13 +3958,13 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>157720</v>
+        <v>157759</v>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr"/>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>2262100 - Erro em praticamente todos os módulos da linha de sala</t>
+          <t>Core/Maker - Regression Test</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -3979,19 +3975,15 @@
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>2262100</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>User Story</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr"/>
@@ -4002,7 +3994,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q3</t>
         </is>
       </c>
       <c r="Q67" s="2" t="n">
@@ -4011,13 +4003,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>157759</v>
+        <v>157762</v>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr"/>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Core/Maker - Regression Test</t>
+          <t>AR - Regression Test</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -4056,32 +4048,40 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>157762</v>
+        <v>157839</v>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr"/>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>AR - Regression Test</t>
+          <t>2262503 - Espessura de Fita de Borda</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>2262503</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Gustavo Garbin de Lima</t>
+        </is>
+      </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>User Story</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr"/>
@@ -4101,13 +4101,13 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>157839</v>
+        <v>158801</v>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>2262503 - Espessura de Fita de Borda</t>
+          <t>2116353 - Wonder Squad - Maker BR - Erro ao enviar para cut pro: Já foi adicionado um item com a mesma chave.</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -4122,14 +4122,14 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2262503</t>
+          <t>2116353</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Garbin de Lima</t>
+          <t>Mauricio Barossi</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4137,7 +4137,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.04; ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -4154,20 +4158,20 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>158801</v>
+        <v>158815</v>
       </c>
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr"/>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>2116353 - Wonder Squad - Maker BR - Erro ao enviar para cut pro: Já foi adicionado um item com a mesma chave.</t>
+          <t xml:space="preserve">** - Wonder - PNP - Professional - Configurador de Dimensões - Falta configuração de cantos em Dormitórios </t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H71" s="2" t="n">
@@ -4175,16 +4179,12 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2116353</t>
+          <t>2117367</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>Mauricio Barossi</t>
-        </is>
-      </c>
+      <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>V.01 R.04; ZendeskTicket</t>
+          <t>NI; ZendeskTicket</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -4211,13 +4211,13 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>158815</v>
+        <v>158885</v>
       </c>
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">** - Wonder - PNP - Professional - Configurador de Dimensões - Falta configuração de cantos em Dormitórios </t>
+          <t>2262211 - Adicionar modelos de Puxadores Duplos</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -4228,26 +4228,26 @@
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2117367</t>
+          <t>2262211</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>NI; ZendeskTicket</t>
-        </is>
-      </c>
+      <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -4264,13 +4264,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>158885</v>
+        <v>158902</v>
       </c>
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>2262211 - Adicionar modelos de Puxadores Duplos</t>
+          <t>** - Wonder - PNP - Essential - Construtor de armários - Sapateiras são inseridas como gavetas</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -4285,22 +4285,22 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2262211</t>
+          <t>2119281</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="N73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>NI; ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -4317,13 +4317,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>158902</v>
+        <v>157751</v>
       </c>
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>** - Wonder - PNP - Essential - Construtor de armários - Sapateiras são inseridas como gavetas</t>
+          <t>Core/Maker - Regression Test</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -4336,24 +4336,16 @@
       <c r="H74" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>2119281</t>
-        </is>
-      </c>
+      <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>NI; ZendeskTicket</t>
-        </is>
-      </c>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -4370,35 +4362,47 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>157751</v>
+        <v>159023</v>
       </c>
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Core/Maker - Regression Test</t>
+          <t xml:space="preserve">** - Wonder - PNP - Modulação - Peças laterais dos montantes não selecionam ao dar duplo clique </t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA Pile</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>2121462</t>
+        </is>
+      </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05; ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -4415,20 +4419,20 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>159023</v>
+        <v>159239</v>
       </c>
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">** - Wonder - PNP - Modulação - Peças laterais dos montantes não selecionam ao dar duplo clique </t>
+          <t>Maker AR - Configurador de Preços - itens sem SKU não permitem salvar preços</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>QA Pile</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H76" s="2" t="n">
@@ -4436,16 +4440,12 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2121462</t>
+          <t>2126515</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>V.01 R.05; ZendeskTicket</t>
+          <t>ZendeskTicket</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -4472,43 +4472,43 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>159239</v>
+        <v>159266</v>
       </c>
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Maker AR - Configurador de Preços - itens sem SKU não permitem salvar preços</t>
+          <t>2259944 - Ajuste Biblioteca Artetílica</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2126515</t>
+          <t xml:space="preserve">2259944 </t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>ZendeskTicket</t>
-        </is>
-      </c>
+      <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q3</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q77" s="2" t="n">
@@ -4525,40 +4525,32 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>159266</v>
+        <v>159562</v>
       </c>
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>2259944 - Ajuste Biblioteca Artetílica</t>
+          <t>Plus - Regression test</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H78" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2259944 </t>
-        </is>
-      </c>
+      <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr"/>
@@ -4569,7 +4561,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q3</t>
         </is>
       </c>
       <c r="Q78" s="2" t="n">
@@ -4578,35 +4570,47 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>159562</v>
+        <v>159874</v>
       </c>
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr"/>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Plus - Regression test</t>
+          <t>** - Wonder - PNP - Modulação - Cozinha Cava - Porta temperos inserido sem porta</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>2327938</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05; ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -4623,47 +4627,35 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>159874</v>
+        <v>134575</v>
       </c>
       <c r="B80" s="2" t="inlineStr"/>
-      <c r="C80" s="2" t="inlineStr"/>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>** - Wonder - PNP - Modulação - Cozinha Cava - Porta temperos inserido sem porta</t>
-        </is>
-      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Exploratorio</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Validating</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>2327938</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>V.01 R.05; ZendeskTicket</t>
-        </is>
-      </c>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -4671,24 +4663,24 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q3</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q80" s="2" t="n">
-        <v>134119</v>
+        <v>124390</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>134575</v>
+        <v>157372</v>
       </c>
       <c r="B81" s="2" t="inlineStr"/>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Exploratorio</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Core/Maker - Erro ao gerar o arquivo para CNC</t>
+        </is>
+      </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
@@ -4705,33 +4697,37 @@
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Exploratório</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Promob\Wonder Squad</t>
+          <t>Promob\Manufacture Team\Builder Squad</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q3</t>
         </is>
       </c>
       <c r="Q81" s="2" t="n">
-        <v>124390</v>
+        <v>134575</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>157372</v>
+        <v>134577</v>
       </c>
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr"/>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Core/Maker - Erro ao gerar o arquivo para CNC</t>
+          <t>BR - Revisar condição DFix em travessas sobrepostas</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -4760,12 +4756,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Promob\Manufacture Team\Builder Squad</t>
+          <t>Promob\Wonder Squad</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q3</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q82" s="2" t="n">
@@ -4774,13 +4770,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>134577</v>
+        <v>135540</v>
       </c>
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr"/>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>BR - Revisar condição DFix em travessas sobrepostas</t>
+          <t>BR - Situações painéis ripados</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -4823,20 +4819,20 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>135540</v>
+        <v>136931</v>
       </c>
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr"/>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>BR - Situações painéis ripados</t>
+          <t>AR - Portas – Espessuras e Redimensionamento</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H84" s="2" t="n">
@@ -4845,7 +4841,11 @@
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Mauricio Barossi</t>
+        </is>
+      </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q84" s="2" t="n">
@@ -4872,20 +4872,20 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>136931</v>
+        <v>136932</v>
       </c>
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr"/>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>AR - Portas – Espessuras e Redimensionamento</t>
+          <t>AR – Portas – Relatórios e Orçamento</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H85" s="2" t="n">
@@ -4894,11 +4894,7 @@
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>Mauricio Barossi</t>
-        </is>
-      </c>
+      <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -4916,7 +4912,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q85" s="2" t="n">
@@ -4925,20 +4921,20 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>136932</v>
+        <v>136934</v>
       </c>
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr"/>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>AR – Portas – Relatórios e Orçamento</t>
+          <t>AR - Portas - Puxadores e Aberturas</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H86" s="2" t="n">
@@ -4947,7 +4943,11 @@
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q86" s="2" t="n">
@@ -4974,20 +4974,20 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>136934</v>
+        <v>137071</v>
       </c>
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr"/>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>AR - Portas - Puxadores e Aberturas</t>
+          <t>BR - Posicionamento Ferragem Uniblock</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H87" s="2" t="n">
@@ -4996,11 +4996,7 @@
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -5018,7 +5014,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q87" s="2" t="n">
@@ -5027,20 +5023,20 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>137071</v>
+        <v>137821</v>
       </c>
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr"/>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>BR - Posicionamento Ferragem Uniblock</t>
+          <t>AR - Face de aplicação do material incorreta nos paineis de portas ripadas ventiladas</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H88" s="2" t="n">
@@ -5049,7 +5045,11 @@
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -5076,20 +5076,20 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>137821</v>
+        <v>139186</v>
       </c>
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr"/>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>AR - Face de aplicação do material incorreta nos paineis de portas ripadas ventiladas</t>
+          <t>BR - Aplicar solução para as gavetas de Cozinhas Cava Madeira</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H89" s="2" t="n">
@@ -5098,11 +5098,7 @@
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -5129,13 +5125,13 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>139186</v>
+        <v>139253</v>
       </c>
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>BR - Aplicar solução para as gavetas de Cozinhas Cava Madeira</t>
+          <t>BR - Situações atributos existentes Deslizantes  - Modelos e Modulação</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -5178,13 +5174,13 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>139253</v>
+        <v>139255</v>
       </c>
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>BR - Situações atributos existentes Deslizantes  - Modelos e Modulação</t>
+          <t>BR - Situações atributos existentes Deslizantes - Orçamento e Relatório de Compras</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -5227,13 +5223,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>139255</v>
+        <v>140171</v>
       </c>
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr"/>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>BR - Situações atributos existentes Deslizantes - Orçamento e Relatório de Compras</t>
+          <t>BR- Testes Estruturas Orçamento Situações já existentes</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
@@ -5267,7 +5263,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2025\Q4</t>
         </is>
       </c>
       <c r="Q92" s="2" t="n">
@@ -5276,20 +5272,20 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>140171</v>
+        <v>140172</v>
       </c>
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr"/>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>BR- Testes Estruturas Orçamento Situações já existentes</t>
+          <t>BR- Referências e Documentações Técnicas</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H93" s="2" t="n">
@@ -5298,7 +5294,11 @@
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Exploratório</t>
+          <t>Exploratório; V.01 R.05</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>Promob\2025\Q4</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q93" s="2" t="n">
@@ -5325,20 +5325,20 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>140172</v>
+        <v>140210</v>
       </c>
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr"/>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>BR- Referências e Documentações Técnicas</t>
+          <t>BR - Salas - Criar portas deslizantes específicas para módulo de Painel</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H94" s="2" t="n">
@@ -5347,11 +5347,7 @@
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -5359,7 +5355,7 @@
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Exploratório; V.01 R.05</t>
+          <t>Exploratório</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
@@ -5369,7 +5365,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q94" s="2" t="n">
@@ -5378,13 +5374,13 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>140210</v>
+        <v>140497</v>
       </c>
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr"/>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>BR - Salas - Criar portas deslizantes específicas para módulo de Painel</t>
+          <t>AR - Ferragens Invertidas - Prateleira Fixa</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -5427,13 +5423,13 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>140497</v>
+        <v>140537</v>
       </c>
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>AR - Ferragens Invertidas - Prateleira Fixa</t>
+          <t>BR/AR - Revisar Junções de Travessas e Puxadores Cava</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -5476,13 +5472,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>140537</v>
+        <v>141384</v>
       </c>
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr"/>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>BR/AR - Revisar Junções de Travessas e Puxadores Cava</t>
+          <t>BR - Exploratórios - Cava Parte II - Situações herdadas</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -5525,13 +5521,13 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>141384</v>
+        <v>141390</v>
       </c>
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr"/>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>BR - Exploratórios - Cava Parte II - Situações herdadas</t>
+          <t>BR - Rework - Cava Parte II</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
@@ -5574,13 +5570,13 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>141390</v>
+        <v>141573</v>
       </c>
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr"/>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>BR - Rework - Cava Parte II</t>
+          <t>AR - Portas Bipartidas</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
@@ -5623,13 +5619,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>141573</v>
+        <v>142169</v>
       </c>
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr"/>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>AR - Portas Bipartidas</t>
+          <t>BR - Melhorias Travessas frontal aquecedor a gás</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -5648,7 +5644,7 @@
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>User Story</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -5672,20 +5668,20 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>142169</v>
+        <v>142256</v>
       </c>
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr"/>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>BR - Melhorias Travessas frontal aquecedor a gás</t>
+          <t>Plus - Portas e Painéis Laterais</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
@@ -5694,10 +5690,14 @@
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>User Story</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -5721,20 +5721,20 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>142256</v>
+        <v>142344</v>
       </c>
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr"/>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Plus - Portas e Painéis Laterais</t>
+          <t>AR - Revisar Portas Basculantes Superiores</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H102" s="2" t="n">
@@ -5743,11 +5743,7 @@
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L102" s="2" t="inlineStr"/>
       <c r="M102" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -5774,20 +5770,20 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>142344</v>
+        <v>143021</v>
       </c>
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr"/>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>AR - Revisar Portas Basculantes Superiores</t>
+          <t>Core/BR - Situações Tampos</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H103" s="2" t="n">
@@ -5796,7 +5792,11 @@
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>Exploratório</t>
+          <t>Exploratório; V.01 R.04</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q103" s="2" t="n">
@@ -5823,20 +5823,20 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>143021</v>
+        <v>143026</v>
       </c>
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="2" t="inlineStr"/>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Core/BR - Situações Tampos</t>
+          <t>BR - Situações já existentes - BR - Max Dimensions I of II</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H104" s="2" t="n">
@@ -5845,11 +5845,7 @@
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L104" s="2" t="inlineStr"/>
       <c r="M104" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -5857,7 +5853,7 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Exploratório; V.01 R.04</t>
+          <t>Exploratório</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
@@ -5867,7 +5863,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q104" s="2" t="n">
@@ -5876,13 +5872,13 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>143026</v>
+        <v>143245</v>
       </c>
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="2" t="inlineStr"/>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>BR - Situações já existentes - BR - Max Dimensions I of II</t>
+          <t>AR  - Caixas Base Superior Línea Gola Madera</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -5925,13 +5921,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>143245</v>
+        <v>143692</v>
       </c>
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr"/>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>AR  - Caixas Base Superior Línea Gola Madera</t>
+          <t>BR - Situações já existentes - BR - Max Dimensions II of II</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -5974,13 +5970,13 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>143692</v>
+        <v>144875</v>
       </c>
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr"/>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>BR - Situações já existentes - BR - Max Dimensions II of II</t>
+          <t>BR - Condição Gavetas - Max Dimensions</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
@@ -6023,13 +6019,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>144875</v>
+        <v>145191</v>
       </c>
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="2" t="inlineStr"/>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>BR - Condição Gavetas - Max Dimensions</t>
+          <t>AR - Fixações Prateleiras Móveis Oficinas</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -6072,13 +6068,13 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>145191</v>
+        <v>145227</v>
       </c>
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="2" t="inlineStr"/>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>AR - Fixações Prateleiras Móveis Oficinas</t>
+          <t>BR - Cantoneiras com posicionamentos de fixadores incorretos / Base de cantoneira curva com dimensionamento incorreto</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -6121,20 +6117,20 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>145227</v>
+        <v>146413</v>
       </c>
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="2" t="inlineStr"/>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>BR - Cantoneiras com posicionamentos de fixadores incorretos / Base de cantoneira curva com dimensionamento incorreto</t>
+          <t>Core/BR - Posicionamento da Travessa L em Cantos L</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
@@ -6143,7 +6139,11 @@
       <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>Exploratório</t>
+          <t>Exploratório; V.01 R.04</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q110" s="2" t="n">
@@ -6170,20 +6170,20 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>146413</v>
+        <v>146449</v>
       </c>
       <c r="B111" s="2" t="inlineStr"/>
       <c r="C111" s="2" t="inlineStr"/>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Core/BR - Posicionamento da Travessa L em Cantos L</t>
+          <t>AR - Posicionamento Puxadores Portas Superiores Línea Gola</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H111" s="2" t="n">
@@ -6192,11 +6192,7 @@
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L111" s="2" t="inlineStr"/>
       <c r="M111" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -6204,7 +6200,7 @@
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Exploratório; V.01 R.04</t>
+          <t>Exploratório</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
@@ -6214,7 +6210,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q111" s="2" t="n">
@@ -6223,13 +6219,13 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>146449</v>
+        <v>146484</v>
       </c>
       <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="2" t="inlineStr"/>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>AR - Posicionamento Puxadores Portas Superiores Línea Gola</t>
+          <t>BR - Situações - 115182 - BR - 45º Milling – Y and Cava Handles</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -6272,13 +6268,13 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>146484</v>
+        <v>146486</v>
       </c>
       <c r="B113" s="2" t="inlineStr"/>
       <c r="C113" s="2" t="inlineStr"/>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>BR - Situações - 115182 - BR - 45º Milling – Y and Cava Handles</t>
+          <t>BR - Desenho Espessuras Portas Perfil Y</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -6321,13 +6317,13 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>146486</v>
+        <v>146610</v>
       </c>
       <c r="B114" s="2" t="inlineStr"/>
       <c r="C114" s="2" t="inlineStr"/>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>BR - Desenho Espessuras Portas Perfil Y</t>
+          <t>AR - Traduções</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -6370,13 +6366,13 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>146610</v>
+        <v>147102</v>
       </c>
       <c r="B115" s="2" t="inlineStr"/>
       <c r="C115" s="2" t="inlineStr"/>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>AR - Traduções</t>
+          <t>AR - Situações Existentes - 142426 - Rear Offset for Base Sides</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -6419,13 +6415,13 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>147102</v>
+        <v>147103</v>
       </c>
       <c r="B116" s="2" t="inlineStr"/>
       <c r="C116" s="2" t="inlineStr"/>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>AR - Situações Existentes - 142426 - Rear Offset for Base Sides</t>
+          <t>AR - Estrutura de Orçamento Puxadores Perfil</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -6468,20 +6464,20 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>147103</v>
+        <v>147333</v>
       </c>
       <c r="B117" s="2" t="inlineStr"/>
       <c r="C117" s="2" t="inlineStr"/>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>AR - Estrutura de Orçamento Puxadores Perfil</t>
+          <t>Plus - Folgas Cantos L Superiores e Bancadas</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H117" s="2" t="n">
@@ -6490,7 +6486,11 @@
       <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q117" s="2" t="n">
@@ -6517,20 +6517,20 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>147333</v>
+        <v>147814</v>
       </c>
       <c r="B118" s="2" t="inlineStr"/>
       <c r="C118" s="2" t="inlineStr"/>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Plus - Folgas Cantos L Superiores e Bancadas</t>
+          <t>BR - Basculantes Serviço de Posicionamento</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H118" s="2" t="n">
@@ -6539,11 +6539,7 @@
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L118" s="2" t="inlineStr"/>
       <c r="M118" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -6561,7 +6557,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q118" s="2" t="n">
@@ -6570,13 +6566,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>147814</v>
+        <v>148502</v>
       </c>
       <c r="B119" s="2" t="inlineStr"/>
       <c r="C119" s="2" t="inlineStr"/>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>BR - Basculantes Serviço de Posicionamento</t>
+          <t>BR - Gavetas Embutidas Eletros</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -6619,13 +6615,13 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>148502</v>
+        <v>148932</v>
       </c>
       <c r="B120" s="2" t="inlineStr"/>
       <c r="C120" s="2" t="inlineStr"/>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>BR - Gavetas Embutidas Eletros</t>
+          <t>BR - Revisar composição laminada da travessa dupla</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -6668,13 +6664,13 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>148932</v>
+        <v>148940</v>
       </c>
       <c r="B121" s="2" t="inlineStr"/>
       <c r="C121" s="2" t="inlineStr"/>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>BR - Revisar composição laminada da travessa dupla</t>
+          <t>BR - Situações Existentes - Double Front Stretchers</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -6717,20 +6713,20 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>148940</v>
+        <v>149329</v>
       </c>
       <c r="B122" s="2" t="inlineStr"/>
       <c r="C122" s="2" t="inlineStr"/>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>BR - Situações Existentes - Double Front Stretchers</t>
+          <t>AR - Línea Gola - Avanço da porta sobre puxador perfil</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H122" s="2" t="n">
@@ -6739,7 +6735,11 @@
       <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q122" s="2" t="n">
@@ -6766,20 +6766,20 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>149329</v>
+        <v>149396</v>
       </c>
       <c r="B123" s="2" t="inlineStr"/>
       <c r="C123" s="2" t="inlineStr"/>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>AR - Línea Gola - Avanço da porta sobre puxador perfil</t>
+          <t>Avanços e recuos das laterais e rodapés</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H123" s="2" t="n">
@@ -6790,7 +6790,7 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>Heloisa Schweizer de Oliveira</t>
+          <t>Jessica Suiani dos Santos Babinski</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q123" s="2" t="n">
@@ -6819,13 +6819,13 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>149396</v>
+        <v>149507</v>
       </c>
       <c r="B124" s="2" t="inlineStr"/>
       <c r="C124" s="2" t="inlineStr"/>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Avanços e recuos das laterais e rodapés</t>
+          <t>AR - Revisar aplicação de fitas de bordas em portas Canto L</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -6841,11 +6841,7 @@
       <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="inlineStr">
-        <is>
-          <t>Jessica Suiani dos Santos Babinski</t>
-        </is>
-      </c>
+      <c r="L124" s="2" t="inlineStr"/>
       <c r="M124" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -6872,13 +6868,13 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>149507</v>
+        <v>149647</v>
       </c>
       <c r="B125" s="2" t="inlineStr"/>
       <c r="C125" s="2" t="inlineStr"/>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>AR - Revisar aplicação de fitas de bordas em portas Canto L</t>
+          <t>BR - Revisar Furos Dobradiças</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -6894,7 +6890,11 @@
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="2" t="inlineStr"/>
       <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>Jessica Suiani dos Santos Babinski</t>
+        </is>
+      </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -6921,13 +6921,13 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>149647</v>
+        <v>149742</v>
       </c>
       <c r="B126" s="2" t="inlineStr"/>
       <c r="C126" s="2" t="inlineStr"/>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>BR - Revisar Furos Dobradiças</t>
+          <t>BR - Redimensionamento Incorreto de Corrediças em módulos com largura inferior a 300 mm</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -6943,11 +6943,7 @@
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="2" t="inlineStr">
-        <is>
-          <t>Jessica Suiani dos Santos Babinski</t>
-        </is>
-      </c>
+      <c r="L126" s="2" t="inlineStr"/>
       <c r="M126" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -6974,13 +6970,13 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>149742</v>
+        <v>149886</v>
       </c>
       <c r="B127" s="2" t="inlineStr"/>
       <c r="C127" s="2" t="inlineStr"/>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>BR - Redimensionamento Incorreto de Corrediças em módulos com largura inferior a 300 mm</t>
+          <t>Plus - Orçamento - Ponteiras Puxador Gola Duplicadas ou Pendentes</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
@@ -7023,20 +7019,20 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>149886</v>
+        <v>149908</v>
       </c>
       <c r="B128" s="2" t="inlineStr"/>
       <c r="C128" s="2" t="inlineStr"/>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Plus - Orçamento - Ponteiras Puxador Gola Duplicadas ou Pendentes</t>
+          <t>Plus - Dobradiças Canto L</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H128" s="2" t="n">
@@ -7045,7 +7041,11 @@
       <c r="I128" s="2" t="inlineStr"/>
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>Vinicius Consorte Vieira</t>
+        </is>
+      </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -7072,20 +7072,20 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>149908</v>
+        <v>150429</v>
       </c>
       <c r="B129" s="2" t="inlineStr"/>
       <c r="C129" s="2" t="inlineStr"/>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Plus - Dobradiças Canto L</t>
+          <t>AR - Fitas de bordas do reforço frontal dos Cantos L - Línea Gola</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H129" s="2" t="n">
@@ -7094,11 +7094,7 @@
       <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="2" t="inlineStr">
-        <is>
-          <t>Vinicius Consorte Vieira</t>
-        </is>
-      </c>
+      <c r="L129" s="2" t="inlineStr"/>
       <c r="M129" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -7125,13 +7121,13 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>150429</v>
+        <v>151070</v>
       </c>
       <c r="B130" s="2" t="inlineStr"/>
       <c r="C130" s="2" t="inlineStr"/>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>AR - Fitas de bordas do reforço frontal dos Cantos L - Línea Gola</t>
+          <t>BR - Ferragens Canto L</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -7174,13 +7170,13 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>151070</v>
+        <v>151849</v>
       </c>
       <c r="B131" s="2" t="inlineStr"/>
       <c r="C131" s="2" t="inlineStr"/>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>BR - Ferragens Canto L</t>
+          <t>BR - *Montantes (Padronizar fórmulas para o modelo de Dor)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
@@ -7223,13 +7219,13 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>151849</v>
+        <v>152002</v>
       </c>
       <c r="B132" s="2" t="inlineStr"/>
       <c r="C132" s="2" t="inlineStr"/>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>BR - *Montantes (Padronizar fórmulas para o modelo de Dor)</t>
+          <t>BR - Referências Incorretas de Afastadores</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -7272,13 +7268,13 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>152002</v>
+        <v>152012</v>
       </c>
       <c r="B133" s="2" t="inlineStr"/>
       <c r="C133" s="2" t="inlineStr"/>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>BR - Referências Incorretas de Afastadores</t>
+          <t>BR - Cozinhas - Medidas de Inserção</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
@@ -7321,13 +7317,13 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>152012</v>
+        <v>152240</v>
       </c>
       <c r="B134" s="2" t="inlineStr"/>
       <c r="C134" s="2" t="inlineStr"/>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>BR - Cozinhas - Medidas de Inserção</t>
+          <t>BR - Gavetas Internas Invisíveis</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -7370,13 +7366,13 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>152240</v>
+        <v>152241</v>
       </c>
       <c r="B135" s="2" t="inlineStr"/>
       <c r="C135" s="2" t="inlineStr"/>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>BR - Gavetas Internas Invisíveis</t>
+          <t>BR - Modelos Gavetas Internas x Sapateiras</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
@@ -7419,13 +7415,13 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>152241</v>
+        <v>152641</v>
       </c>
       <c r="B136" s="2" t="inlineStr"/>
       <c r="C136" s="2" t="inlineStr"/>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>BR - Modelos Gavetas Internas x Sapateiras</t>
+          <t>AR / BR - Revisar folgas gavetas internas com frentes e sem frentes</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
@@ -7468,20 +7464,20 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>152641</v>
+        <v>152952</v>
       </c>
       <c r="B137" s="2" t="inlineStr"/>
       <c r="C137" s="2" t="inlineStr"/>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>AR / BR - Revisar folgas gavetas internas com frentes e sem frentes</t>
+          <t>AR - Alinhamento Puxadores Madera</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA Pile</t>
         </is>
       </c>
       <c r="H137" s="2" t="n">
@@ -7490,7 +7486,11 @@
       <c r="I137" s="2" t="inlineStr"/>
       <c r="J137" s="2" t="inlineStr"/>
       <c r="K137" s="2" t="inlineStr"/>
-      <c r="L137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>Vinicius Consorte Vieira</t>
+        </is>
+      </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q137" s="2" t="n">
@@ -7517,20 +7517,20 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>152952</v>
+        <v>153364</v>
       </c>
       <c r="B138" s="2" t="inlineStr"/>
       <c r="C138" s="2" t="inlineStr"/>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>AR - Alinhamento Puxadores Madera</t>
+          <t>BR - Slides incoerentes - Maker BR</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H138" s="2" t="n">
@@ -7570,13 +7570,13 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>153364</v>
+        <v>153371</v>
       </c>
       <c r="B139" s="2" t="inlineStr"/>
       <c r="C139" s="2" t="inlineStr"/>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>BR - Slides incoerentes - Maker BR</t>
+          <t>BR - Linha Gola - Altos - core</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
@@ -7623,20 +7623,20 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>153371</v>
+        <v>153769</v>
       </c>
       <c r="B140" s="2" t="inlineStr"/>
       <c r="C140" s="2" t="inlineStr"/>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>BR - Linha Gola - Altos - core</t>
+          <t>Plus - Ajustar DXF Portas Laterais</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H140" s="2" t="n">
@@ -7645,11 +7645,7 @@
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="2" t="inlineStr">
-        <is>
-          <t>Vinicius Consorte Vieira</t>
-        </is>
-      </c>
+      <c r="L140" s="2" t="inlineStr"/>
       <c r="M140" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -7667,7 +7663,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q140" s="2" t="n">
@@ -7676,13 +7672,13 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>153769</v>
+        <v>153883</v>
       </c>
       <c r="B141" s="2" t="inlineStr"/>
       <c r="C141" s="2" t="inlineStr"/>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plus - Ajustar DXF Portas Laterais</t>
+          <t>Plus - Dobradiças não são inseridas</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr"/>
@@ -7725,13 +7721,13 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>153883</v>
+        <v>153933</v>
       </c>
       <c r="B142" s="2" t="inlineStr"/>
       <c r="C142" s="2" t="inlineStr"/>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plus - Dobradiças não são inseridas</t>
+          <t>Core/Start/Maker - Ajustar altura máxima corpos de gavetas</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
@@ -7774,13 +7770,13 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>153933</v>
+        <v>153958</v>
       </c>
       <c r="B143" s="2" t="inlineStr"/>
       <c r="C143" s="2" t="inlineStr"/>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Core/Start/Maker - Ajustar altura máxima corpos de gavetas</t>
+          <t>AR - Eletros respeitam folgas de Bajos</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr"/>
@@ -7823,13 +7819,13 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>153958</v>
+        <v>154371</v>
       </c>
       <c r="B144" s="2" t="inlineStr"/>
       <c r="C144" s="2" t="inlineStr"/>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>AR - Eletros respeitam folgas de Bajos</t>
+          <t>AR - Ajustar Folgas em Tall + Divisórias</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr"/>
@@ -7863,7 +7859,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q144" s="2" t="n">
@@ -7872,13 +7868,13 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>154371</v>
+        <v>154451</v>
       </c>
       <c r="B145" s="2" t="inlineStr"/>
       <c r="C145" s="2" t="inlineStr"/>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>AR - Ajustar Folgas em Tall + Divisórias</t>
+          <t>AR - Gavetas de Cocinas Gola Madera são inseridas sem frente</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr"/>
@@ -7912,7 +7908,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q145" s="2" t="n">
@@ -7921,13 +7917,13 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>154451</v>
+        <v>154579</v>
       </c>
       <c r="B146" s="2" t="inlineStr"/>
       <c r="C146" s="2" t="inlineStr"/>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>AR - Gavetas de Cocinas Gola Madera são inseridas sem frente</t>
+          <t>Core/Maker BR - Junções Travessas L travam Promob</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
@@ -7970,20 +7966,20 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>154579</v>
+        <v>154581</v>
       </c>
       <c r="B147" s="2" t="inlineStr"/>
       <c r="C147" s="2" t="inlineStr"/>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Core/Maker BR - Junções Travessas L travam Promob</t>
+          <t>Core/Maker BR - Orçamento Tampos Madeira</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H147" s="2" t="n">
@@ -7992,7 +7988,11 @@
       <c r="I147" s="2" t="inlineStr"/>
       <c r="J147" s="2" t="inlineStr"/>
       <c r="K147" s="2" t="inlineStr"/>
-      <c r="L147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>Exploratório</t>
+          <t>Exploratório; V.01 R.05</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q3</t>
         </is>
       </c>
       <c r="Q147" s="2" t="n">
@@ -8019,20 +8019,20 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>154581</v>
+        <v>154869</v>
       </c>
       <c r="B148" s="2" t="inlineStr"/>
       <c r="C148" s="2" t="inlineStr"/>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Core/Maker BR - Orçamento Tampos Madeira</t>
+          <t>Core/Maker - Folgas de Frentes e Portas</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H148" s="2" t="n">
@@ -8041,11 +8041,7 @@
       <c r="I148" s="2" t="inlineStr"/>
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L148" s="2" t="inlineStr"/>
       <c r="M148" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -8053,7 +8049,7 @@
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>Exploratório; V.01 R.05</t>
+          <t>Exploratório</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
@@ -8063,7 +8059,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q3</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q148" s="2" t="n">
@@ -8072,13 +8068,13 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>154869</v>
+        <v>154898</v>
       </c>
       <c r="B149" s="2" t="inlineStr"/>
       <c r="C149" s="2" t="inlineStr"/>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Core/Maker - Folgas de Frentes e Portas</t>
+          <t>Core/BR - Hierarquia de Ferragens Incorreta em Orçamento</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr"/>
@@ -8121,20 +8117,20 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>154898</v>
+        <v>150549</v>
       </c>
       <c r="B150" s="2" t="inlineStr"/>
       <c r="C150" s="2" t="inlineStr"/>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Core/BR - Hierarquia de Ferragens Incorreta em Orçamento</t>
+          <t>AR - Padronizar todos os puxadores com a mesma nomeclatura</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H150" s="2" t="n">
@@ -8143,7 +8139,11 @@
       <c r="I150" s="2" t="inlineStr"/>
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q150" s="2" t="n">
@@ -8170,20 +8170,20 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>150549</v>
+        <v>155496</v>
       </c>
       <c r="B151" s="2" t="inlineStr"/>
       <c r="C151" s="2" t="inlineStr"/>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>AR - Padronizar todos os puxadores com a mesma nomeclatura</t>
+          <t>AR - Fitas de Bordas Torres Eletros</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H151" s="2" t="n">
@@ -8192,11 +8192,7 @@
       <c r="I151" s="2" t="inlineStr"/>
       <c r="J151" s="2" t="inlineStr"/>
       <c r="K151" s="2" t="inlineStr"/>
-      <c r="L151" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L151" s="2" t="inlineStr"/>
       <c r="M151" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -8214,7 +8210,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q151" s="2" t="n">
@@ -8223,13 +8219,13 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>155496</v>
+        <v>155497</v>
       </c>
       <c r="B152" s="2" t="inlineStr"/>
       <c r="C152" s="2" t="inlineStr"/>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>AR - Fitas de Bordas Torres Eletros</t>
+          <t>AR - Fixações Torres Eletros</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
@@ -8272,13 +8268,13 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>155497</v>
+        <v>155499</v>
       </c>
       <c r="B153" s="2" t="inlineStr"/>
       <c r="C153" s="2" t="inlineStr"/>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>AR - Fixações Torres Eletros</t>
+          <t>Core/BR - Montantes gaveteiros</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
@@ -8321,13 +8317,13 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>155499</v>
+        <v>156306</v>
       </c>
       <c r="B154" s="2" t="inlineStr"/>
       <c r="C154" s="2" t="inlineStr"/>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Core/BR - Montantes gaveteiros</t>
+          <t>Pias - Travessa Traseira Não é Inserida</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
@@ -8370,13 +8366,13 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>156306</v>
+        <v>156419</v>
       </c>
       <c r="B155" s="2" t="inlineStr"/>
       <c r="C155" s="2" t="inlineStr"/>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Pias - Travessa Traseira Não é Inserida</t>
+          <t>AR - Línea Gola - Dimensionamento Puxadores Madera</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
@@ -8419,13 +8415,13 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>156419</v>
+        <v>156603</v>
       </c>
       <c r="B156" s="2" t="inlineStr"/>
       <c r="C156" s="2" t="inlineStr"/>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>AR - Línea Gola - Dimensionamento Puxadores Madera</t>
+          <t>Core - Correções Modelos Parceiros</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
@@ -8459,7 +8455,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q3</t>
         </is>
       </c>
       <c r="Q156" s="2" t="n">
@@ -8468,20 +8464,20 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>156603</v>
+        <v>153320</v>
       </c>
       <c r="B157" s="2" t="inlineStr"/>
       <c r="C157" s="2" t="inlineStr"/>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Core - Correções Modelos Parceiros</t>
+          <t>BR - Slides incoerentes - Core</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H157" s="2" t="n">
@@ -8490,7 +8486,11 @@
       <c r="I157" s="2" t="inlineStr"/>
       <c r="J157" s="2" t="inlineStr"/>
       <c r="K157" s="2" t="inlineStr"/>
-      <c r="L157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Exploratório</t>
+          <t>Exploratório; V.01 R.04</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q3</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q157" s="2" t="n">
@@ -8517,20 +8517,20 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>153320</v>
+        <v>157066</v>
       </c>
       <c r="B158" s="2" t="inlineStr"/>
       <c r="C158" s="2" t="inlineStr"/>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>BR - Slides incoerentes - Core</t>
+          <t>AR - Revisar face de inserção do fixador da lateral módulo Esq Recto Der - Islas</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H158" s="2" t="n">
@@ -8539,11 +8539,7 @@
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
-      <c r="L158" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L158" s="2" t="inlineStr"/>
       <c r="M158" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -8551,7 +8547,7 @@
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>Exploratório; V.01 R.04</t>
+          <t>Exploratório</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
@@ -8570,13 +8566,13 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>157066</v>
+        <v>157151</v>
       </c>
       <c r="B159" s="2" t="inlineStr"/>
       <c r="C159" s="2" t="inlineStr"/>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>AR - Revisar face de inserção do fixador da lateral módulo Esq Recto Der - Islas</t>
+          <t>Plus - Espessuras prateleiras de módulos linkados com o construtor</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
@@ -8610,7 +8606,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q3</t>
         </is>
       </c>
       <c r="Q159" s="2" t="n">
@@ -8619,13 +8615,13 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>157151</v>
+        <v>157636</v>
       </c>
       <c r="B160" s="2" t="inlineStr"/>
       <c r="C160" s="2" t="inlineStr"/>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Plus - Espessuras prateleiras de módulos linkados com o construtor</t>
+          <t>AR - Orçamento Tampos Madeira</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr"/>
@@ -8659,7 +8655,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q3</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q160" s="2" t="n">
@@ -8668,13 +8664,13 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>157636</v>
+        <v>157850</v>
       </c>
       <c r="B161" s="2" t="inlineStr"/>
       <c r="C161" s="2" t="inlineStr"/>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>AR - Orçamento Tampos Madeira</t>
+          <t>Core/BR - Revisar FOLPAI não exibindo no orçamento de itens e peças avulsas</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
@@ -8717,13 +8713,13 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>157850</v>
+        <v>158646</v>
       </c>
       <c r="B162" s="2" t="inlineStr"/>
       <c r="C162" s="2" t="inlineStr"/>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Core/BR - Revisar FOLPAI não exibindo no orçamento de itens e peças avulsas</t>
+          <t>Plus - Edição de Preços Indisponível</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
@@ -8757,7 +8753,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q3</t>
         </is>
       </c>
       <c r="Q162" s="2" t="n">
@@ -8766,13 +8762,13 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>158646</v>
+        <v>158895</v>
       </c>
       <c r="B163" s="2" t="inlineStr"/>
       <c r="C163" s="2" t="inlineStr"/>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Plus - Edição de Preços Indisponível</t>
+          <t>AR - Adega Nicho não tem Travessa Traseira</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
@@ -8806,7 +8802,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q3</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q163" s="2" t="n">
@@ -8815,13 +8811,13 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>158895</v>
+        <v>158928</v>
       </c>
       <c r="B164" s="2" t="inlineStr"/>
       <c r="C164" s="2" t="inlineStr"/>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>AR - Adega Nicho não tem Travessa Traseira</t>
+          <t>AR - Travessas superiores não são desabilitadas</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
@@ -8864,13 +8860,13 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>158928</v>
+        <v>158949</v>
       </c>
       <c r="B165" s="2" t="inlineStr"/>
       <c r="C165" s="2" t="inlineStr"/>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>AR - Travessas superiores não são desabilitadas</t>
+          <t>AR - Dobradiça Rotacionada</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
@@ -8913,20 +8909,20 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>158949</v>
+        <v>155559</v>
       </c>
       <c r="B166" s="2" t="inlineStr"/>
       <c r="C166" s="2" t="inlineStr"/>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>AR - Dobradiça Rotacionada</t>
+          <t>Core/BR - Vidros - Configurador de Preços</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H166" s="2" t="n">
@@ -8935,7 +8931,11 @@
       <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>Heloisa Schweizer de Oliveira</t>
+        </is>
+      </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q166" s="2" t="n">
@@ -8962,20 +8962,20 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>155559</v>
+        <v>143025</v>
       </c>
       <c r="B167" s="2" t="inlineStr"/>
       <c r="C167" s="2" t="inlineStr"/>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Core/BR - Vidros - Configurador de Preços</t>
+          <t>Melhorias - BR - Max Dimensions I of II</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H167" s="2" t="n">
@@ -8984,14 +8984,10 @@
       <c r="I167" s="2" t="inlineStr"/>
       <c r="J167" s="2" t="inlineStr"/>
       <c r="K167" s="2" t="inlineStr"/>
-      <c r="L167" s="2" t="inlineStr">
-        <is>
-          <t>Heloisa Schweizer de Oliveira</t>
-        </is>
-      </c>
+      <c r="L167" s="2" t="inlineStr"/>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -9006,7 +9002,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q167" s="2" t="n">
@@ -9015,13 +9011,13 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>143025</v>
+        <v>158988</v>
       </c>
       <c r="B168" s="2" t="inlineStr"/>
       <c r="C168" s="2" t="inlineStr"/>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Melhorias - BR - Max Dimensions I of II</t>
+          <t>AR - Travessa traseira módulo de coluna/viga</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
@@ -9040,7 +9036,7 @@
       <c r="L168" s="2" t="inlineStr"/>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -9064,13 +9060,13 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>158988</v>
+        <v>159081</v>
       </c>
       <c r="B169" s="2" t="inlineStr"/>
       <c r="C169" s="2" t="inlineStr"/>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>AR - Travessa traseira módulo de coluna/viga</t>
+          <t>AR - Construtor de Armários - Armário Superior Dormitórios - Espessuras não são consideradas Armário Superior</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
@@ -9113,13 +9109,13 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>159081</v>
+        <v>159337</v>
       </c>
       <c r="B170" s="2" t="inlineStr"/>
       <c r="C170" s="2" t="inlineStr"/>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>AR - Construtor de Armários - Armário Superior Dormitórios - Espessuras não são consideradas Armário Superior</t>
+          <t>Core/Maker - Fitas de Bordas X Sobrecorte - Peças Irregulares</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
@@ -9162,13 +9158,13 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>159337</v>
+        <v>159677</v>
       </c>
       <c r="B171" s="2" t="inlineStr"/>
       <c r="C171" s="2" t="inlineStr"/>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Core/Maker - Fitas de Bordas X Sobrecorte - Peças Irregulares</t>
+          <t>AR - Cantos Suportes Metálicos</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
@@ -9190,11 +9186,7 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>Exploratório</t>
-        </is>
-      </c>
+      <c r="N171" s="2" t="inlineStr"/>
       <c r="O171" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -9211,13 +9203,13 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>159677</v>
+        <v>160127</v>
       </c>
       <c r="B172" s="2" t="inlineStr"/>
       <c r="C172" s="2" t="inlineStr"/>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>AR - Cantos Suportes Metálicos</t>
+          <t>Core/BR - Situações Cantos L e Oblíquos</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
@@ -9256,13 +9248,13 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>160127</v>
+        <v>160226</v>
       </c>
       <c r="B173" s="2" t="inlineStr"/>
       <c r="C173" s="2" t="inlineStr"/>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Core/BR - Situações Cantos L e Oblíquos</t>
+          <t>AR - Plano de Corte Não é Gerado</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
@@ -9292,7 +9284,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q3</t>
         </is>
       </c>
       <c r="Q173" s="2" t="n">
@@ -9301,15 +9293,15 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>160226</v>
+        <v>134127</v>
       </c>
       <c r="B174" s="2" t="inlineStr"/>
-      <c r="C174" s="2" t="inlineStr"/>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>AR - Plano de Corte Não é Gerado</t>
-        </is>
-      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Concluídas</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr"/>
       <c r="E174" s="2" t="inlineStr"/>
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="2" t="inlineStr">
@@ -9326,7 +9318,7 @@
       <c r="L174" s="2" t="inlineStr"/>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr"/>
@@ -9337,29 +9329,29 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q3</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q174" s="2" t="n">
-        <v>134575</v>
+        <v>124390</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>134127</v>
+        <v>137310</v>
       </c>
       <c r="B175" s="2" t="inlineStr"/>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>Concluídas</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr"/>
+      <c r="C175" s="2" t="inlineStr"/>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>BR - Guias de Produto - Revisar Slides Linha Cava</t>
+        </is>
+      </c>
       <c r="E175" s="2" t="inlineStr"/>
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H175" s="2" t="n">
@@ -9368,10 +9360,14 @@
       <c r="I175" s="2" t="inlineStr"/>
       <c r="J175" s="2" t="inlineStr"/>
       <c r="K175" s="2" t="inlineStr"/>
-      <c r="L175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>Jessica Suiani dos Santos Babinski</t>
+        </is>
+      </c>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="N175" s="2" t="inlineStr"/>
@@ -9386,18 +9382,18 @@
         </is>
       </c>
       <c r="Q175" s="2" t="n">
-        <v>124390</v>
+        <v>134127</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>137310</v>
+        <v>149726</v>
       </c>
       <c r="B176" s="2" t="inlineStr"/>
       <c r="C176" s="2" t="inlineStr"/>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>BR - Guias de Produto - Revisar Slides Linha Cava</t>
+          <t>2256219 - Erros nos Painéis de Sala</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
@@ -9410,7 +9406,11 @@
       <c r="H176" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>2256219</t>
+        </is>
+      </c>
       <c r="J176" s="2" t="inlineStr"/>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q176" s="2" t="n">
@@ -9440,13 +9440,13 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>149726</v>
+        <v>150742</v>
       </c>
       <c r="B177" s="2" t="inlineStr"/>
       <c r="C177" s="2" t="inlineStr"/>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>2256219 - Erros nos Painéis de Sala</t>
+          <t>1927804 - Módulos de dormitório com divisão</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
@@ -9461,22 +9461,22 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>2256219</t>
+          <t>1927804</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr"/>
       <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="2" t="inlineStr">
-        <is>
-          <t>Jessica Suiani dos Santos Babinski</t>
-        </is>
-      </c>
+      <c r="L177" s="2" t="inlineStr"/>
       <c r="M177" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="N177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>NI; ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -9493,13 +9493,13 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>150742</v>
+        <v>142857</v>
       </c>
       <c r="B178" s="2" t="inlineStr"/>
       <c r="C178" s="2" t="inlineStr"/>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>1927804 - Módulos de dormitório com divisão</t>
+          <t>2251044 - Promob Maker BR - Orçamento - 'itens sem preço' mesmo com valor cadastrado no configurador de preços</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
@@ -9514,22 +9514,22 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>1927804</t>
+          <t xml:space="preserve">2251044 </t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr"/>
       <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>Mauricio Barossi</t>
+        </is>
+      </c>
       <c r="M178" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="N178" s="2" t="inlineStr">
-        <is>
-          <t>NI; ZendeskTicket</t>
-        </is>
-      </c>
+      <c r="N178" s="2" t="inlineStr"/>
       <c r="O178" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob\2026\Q1</t>
         </is>
       </c>
       <c r="Q178" s="2" t="n">
@@ -9546,13 +9546,13 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>142857</v>
+        <v>134206</v>
       </c>
       <c r="B179" s="2" t="inlineStr"/>
       <c r="C179" s="2" t="inlineStr"/>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>2251044 - Promob Maker BR - Orçamento - 'itens sem preço' mesmo com valor cadastrado no configurador de preços</t>
+          <t>Revisar imagem rasgo em itens de Componentes</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
@@ -9565,16 +9565,12 @@
       <c r="H179" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I179" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2251044 </t>
-        </is>
-      </c>
+      <c r="I179" s="2" t="inlineStr"/>
       <c r="J179" s="2" t="inlineStr"/>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Barossi</t>
+          <t>Jessica Suiani dos Santos Babinski</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
@@ -9590,7 +9586,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q1</t>
+          <t>Promob\2025\Q3</t>
         </is>
       </c>
       <c r="Q179" s="2" t="n">
@@ -9599,13 +9595,13 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>134206</v>
+        <v>134210</v>
       </c>
       <c r="B180" s="2" t="inlineStr"/>
       <c r="C180" s="2" t="inlineStr"/>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Revisar imagem rasgo em itens de Componentes</t>
+          <t>Valor do Atributo Diferente na Condição de Visibilidade</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr"/>
@@ -9623,7 +9619,7 @@
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>Jessica Suiani dos Santos Babinski</t>
+          <t>Mauricio Barossi</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
@@ -9648,13 +9644,13 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>134210</v>
+        <v>134211</v>
       </c>
       <c r="B181" s="2" t="inlineStr"/>
       <c r="C181" s="2" t="inlineStr"/>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Valor do Atributo Diferente na Condição de Visibilidade</t>
+          <t>Inconformidade gaveteiro Blum</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr"/>
@@ -9697,13 +9693,13 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>134211</v>
+        <v>134232</v>
       </c>
       <c r="B182" s="2" t="inlineStr"/>
       <c r="C182" s="2" t="inlineStr"/>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Inconformidade gaveteiro Blum</t>
+          <t>2242040 - Atributo deslocamento de ranhura indisponível</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr"/>
@@ -9714,14 +9710,18 @@
         </is>
       </c>
       <c r="H182" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I182" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2242040 </t>
+        </is>
+      </c>
       <c r="J182" s="2" t="inlineStr"/>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Barossi</t>
+          <t>Jessica Suiani dos Santos Babinski</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr">
@@ -9746,13 +9746,13 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>134232</v>
+        <v>151561</v>
       </c>
       <c r="B183" s="2" t="inlineStr"/>
       <c r="C183" s="2" t="inlineStr"/>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>2242040 - Atributo deslocamento de ranhura indisponível</t>
+          <t>2257580 - Usinagem Avulsa Retangular</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr"/>
@@ -9763,18 +9763,18 @@
         </is>
       </c>
       <c r="H183" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2242040 </t>
+          <t>2257580</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr"/>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>Jessica Suiani dos Santos Babinski</t>
+          <t>Mauricio Barossi</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>Promob\2025\Q3</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q183" s="2" t="n">
@@ -9799,13 +9799,13 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>151561</v>
+        <v>149775</v>
       </c>
       <c r="B184" s="2" t="inlineStr"/>
       <c r="C184" s="2" t="inlineStr"/>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>2257580 - Usinagem Avulsa Retangular</t>
+          <t>Problemas com orçamento - NaN</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr"/>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>2257580</t>
+          <t>1896101</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr"/>
@@ -9835,7 +9835,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N184" s="2" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>NI; ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -9852,13 +9856,13 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>149775</v>
+        <v>150455</v>
       </c>
       <c r="B185" s="2" t="inlineStr"/>
       <c r="C185" s="2" t="inlineStr"/>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Problemas com orçamento - NaN</t>
+          <t>2256502 - Erros nos módulos inferiores de Dormitórios</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
@@ -9873,7 +9877,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>1896101</t>
+          <t>2256502</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr"/>
@@ -9888,11 +9892,7 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N185" s="2" t="inlineStr">
-        <is>
-          <t>NI; ZendeskTicket</t>
-        </is>
-      </c>
+      <c r="N185" s="2" t="inlineStr"/>
       <c r="O185" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -9909,13 +9909,13 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>150455</v>
+        <v>142939</v>
       </c>
       <c r="B186" s="2" t="inlineStr"/>
       <c r="C186" s="2" t="inlineStr"/>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>2256502 - Erros nos módulos inferiores de Dormitórios</t>
+          <t>2251072 - Promob Maker BR - Modulação/Modelos - Afastador gaveta interna Montante 4 desconfigurado</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
@@ -9930,14 +9930,14 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>2256502</t>
+          <t>2251072</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr"/>
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Barossi</t>
+          <t>Jessica Suiani dos Santos Babinski</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob\2026\Q1</t>
         </is>
       </c>
       <c r="Q186" s="2" t="n">
@@ -9962,13 +9962,13 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>142939</v>
+        <v>150430</v>
       </c>
       <c r="B187" s="2" t="inlineStr"/>
       <c r="C187" s="2" t="inlineStr"/>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2251072 - Promob Maker BR - Modulação/Modelos - Afastador gaveta interna Montante 4 desconfigurado</t>
+          <t>Maker AR - Inconformidade Expression em módulos da Linha Gola</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>2251072</t>
+          <t>1919517</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr"/>
@@ -9998,7 +9998,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N187" s="2" t="inlineStr"/>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -10006,7 +10010,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q1</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q187" s="2" t="n">
@@ -10015,13 +10019,13 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>150430</v>
+        <v>151718</v>
       </c>
       <c r="B188" s="2" t="inlineStr"/>
       <c r="C188" s="2" t="inlineStr"/>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Maker AR - Inconformidade Expression em módulos da Linha Gola</t>
+          <t>2257161 - Cadastro Usinagem Cava Madeira</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr"/>
@@ -10036,14 +10040,14 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>1919517</t>
+          <t>2257161</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr"/>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>Jessica Suiani dos Santos Babinski</t>
+          <t>Mauricio Barossi</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr">
@@ -10051,11 +10055,7 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N188" s="2" t="inlineStr">
-        <is>
-          <t>ZendeskTicket</t>
-        </is>
-      </c>
+      <c r="N188" s="2" t="inlineStr"/>
       <c r="O188" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -10072,13 +10072,13 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>151718</v>
+        <v>143287</v>
       </c>
       <c r="B189" s="2" t="inlineStr"/>
       <c r="C189" s="2" t="inlineStr"/>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>2257161 - Cadastro Usinagem Cava Madeira</t>
+          <t>2251343 - Armário de coluna - Fita frontal da lateral posicionada para baixo</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr"/>
@@ -10091,16 +10091,12 @@
       <c r="H189" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I189" s="2" t="inlineStr">
-        <is>
-          <t>2257161</t>
-        </is>
-      </c>
+      <c r="I189" s="2" t="inlineStr"/>
       <c r="J189" s="2" t="inlineStr"/>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Barossi</t>
+          <t>Bruna Scortegagna Rodrigues</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr">
@@ -10116,7 +10112,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob\2026\Q1</t>
         </is>
       </c>
       <c r="Q189" s="2" t="n">
@@ -10125,13 +10121,13 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>143287</v>
+        <v>147671</v>
       </c>
       <c r="B190" s="2" t="inlineStr"/>
       <c r="C190" s="2" t="inlineStr"/>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>2251343 - Armário de coluna - Fita frontal da lateral posicionada para baixo</t>
+          <t>Pnp - Fitas de Bordas Caixa - Cozinha</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr"/>
@@ -10149,7 +10145,7 @@
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>Bruna Scortegagna Rodrigues</t>
+          <t>Guilherme Fernandes da Silva</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr">
@@ -10165,7 +10161,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q1</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q190" s="2" t="n">
@@ -10174,13 +10170,13 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>147671</v>
+        <v>141389</v>
       </c>
       <c r="B191" s="2" t="inlineStr"/>
       <c r="C191" s="2" t="inlineStr"/>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Pnp - Fitas de Bordas Caixa - Cozinha</t>
+          <t>2249698 - Promob Maker Br - Configurador de dimensões - Afastamento traseiro nichos</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr"/>
@@ -10193,12 +10189,16 @@
       <c r="H191" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I191" s="2" t="inlineStr"/>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>2249698</t>
+        </is>
+      </c>
       <c r="J191" s="2" t="inlineStr"/>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Fernandes da Silva</t>
+          <t>Jessica Suiani dos Santos Babinski</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob\2026\Q1</t>
         </is>
       </c>
       <c r="Q191" s="2" t="n">
@@ -10223,13 +10223,13 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>141389</v>
+        <v>149529</v>
       </c>
       <c r="B192" s="2" t="inlineStr"/>
       <c r="C192" s="2" t="inlineStr"/>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2249698 - Promob Maker Br - Configurador de dimensões - Afastamento traseiro nichos</t>
+          <t>** - Wonder - Maker Br - Dormitórios/Altos/Armários - Itens inserindo com prateleiras internas desconfiguradas</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr"/>
@@ -10244,14 +10244,14 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>2249698</t>
+          <t>1896100</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr"/>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>Jessica Suiani dos Santos Babinski</t>
+          <t>Mauricio Barossi</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr">
@@ -10259,7 +10259,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -10267,7 +10271,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q1</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q192" s="2" t="n">
@@ -10276,13 +10280,13 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>149529</v>
+        <v>143296</v>
       </c>
       <c r="B193" s="2" t="inlineStr"/>
       <c r="C193" s="2" t="inlineStr"/>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>** - Wonder - Maker Br - Dormitórios/Altos/Armários - Itens inserindo com prateleiras internas desconfiguradas</t>
+          <t>2251333 - Promob Maker Br - Módulo Canto L Esquerdo - Base superior com folga frontal</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr"/>
@@ -10297,14 +10301,14 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>1896100</t>
+          <t>2251333</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr"/>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Barossi</t>
+          <t>Bruna Scortegagna Rodrigues</t>
         </is>
       </c>
       <c r="M193" s="2" t="inlineStr">
@@ -10312,11 +10316,7 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N193" s="2" t="inlineStr">
-        <is>
-          <t>ZendeskTicket</t>
-        </is>
-      </c>
+      <c r="N193" s="2" t="inlineStr"/>
       <c r="O193" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob\2026\Q1</t>
         </is>
       </c>
       <c r="Q193" s="2" t="n">
@@ -10333,13 +10333,13 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>143296</v>
+        <v>151329</v>
       </c>
       <c r="B194" s="2" t="inlineStr"/>
       <c r="C194" s="2" t="inlineStr"/>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>2251333 - Promob Maker Br - Módulo Canto L Esquerdo - Base superior com folga frontal</t>
+          <t>* -  Wonder Squad - Maker AR - Armário é inserido com duas prateleiras</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr"/>
@@ -10354,14 +10354,14 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>2251333</t>
+          <t>1946532</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr"/>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>Bruna Scortegagna Rodrigues</t>
+          <t>Mauricio Barossi</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
@@ -10369,7 +10369,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -10377,7 +10381,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q1</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q194" s="2" t="n">
@@ -10386,13 +10390,13 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>151329</v>
+        <v>150454</v>
       </c>
       <c r="B195" s="2" t="inlineStr"/>
       <c r="C195" s="2" t="inlineStr"/>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>* -  Wonder Squad - Maker AR - Armário é inserido com duas prateleiras</t>
+          <t>2256619 - Profundidade de inserção de gavetas e sapateiras</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr"/>
@@ -10407,14 +10411,14 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>1946532</t>
+          <t>2256619</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr"/>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Barossi</t>
+          <t>Guilherme Fernandes da Silva</t>
         </is>
       </c>
       <c r="M195" s="2" t="inlineStr">
@@ -10422,11 +10426,7 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N195" s="2" t="inlineStr">
-        <is>
-          <t>ZendeskTicket</t>
-        </is>
-      </c>
+      <c r="N195" s="2" t="inlineStr"/>
       <c r="O195" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -10443,13 +10443,13 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>150454</v>
+        <v>149321</v>
       </c>
       <c r="B196" s="2" t="inlineStr"/>
       <c r="C196" s="2" t="inlineStr"/>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>2256619 - Profundidade de inserção de gavetas e sapateiras</t>
+          <t>Feature Configurator incorrectly defaults edge tape height to 25mm plate condition when plate thickness variation is set to 0.1mm</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr"/>
@@ -10464,14 +10464,14 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>2256619</t>
+          <t>E-desk: 2255916</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr"/>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Fernandes da Silva</t>
+          <t>Daniel Botogoske</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr">
@@ -10479,15 +10479,19 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>#2026-Q1; Catalog - 5.60.1.94 (Apr/26); Connect V2 - 2.2.32.0 (Mar/26); InternalTicket; March; Product: Promob; Promob - 5.60.45.4 (Mar/26); Wizards of Bugs</t>
+        </is>
+      </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
-          <t>Promob\Wonder Squad</t>
+          <t>Promob\Promob Squad</t>
         </is>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob\2026\Q2\S13-26 (15-JUN to 26-JUN)</t>
         </is>
       </c>
       <c r="Q196" s="2" t="n">
@@ -10496,16 +10500,16 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>149321</v>
+        <v>153173</v>
       </c>
       <c r="B197" s="2" t="inlineStr"/>
       <c r="C197" s="2" t="inlineStr"/>
-      <c r="D197" s="2" t="inlineStr">
-        <is>
-          <t>Feature Configurator incorrectly defaults edge tape height to 25mm plate condition when plate thickness variation is set to 0.1mm</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr"/>
+      <c r="D197" s="2" t="inlineStr"/>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
       <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr">
         <is>
@@ -10515,11 +10519,7 @@
       <c r="H197" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I197" s="2" t="inlineStr">
-        <is>
-          <t>E-desk: 2255916</t>
-        </is>
-      </c>
+      <c r="I197" s="2" t="inlineStr"/>
       <c r="J197" s="2" t="inlineStr"/>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr">
@@ -10529,14 +10529,10 @@
       </c>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="N197" s="2" t="inlineStr">
-        <is>
-          <t>#2026-Q1; Catalog - 5.60.1.94 (Apr/26); Connect V2 - 2.2.32.0 (Mar/26); InternalTicket; March; Product: Promob; Promob - 5.60.45.4 (Mar/26); Wizards of Bugs</t>
-        </is>
-      </c>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr"/>
       <c r="O197" s="2" t="inlineStr">
         <is>
           <t>Promob\Promob Squad</t>
@@ -10548,21 +10544,21 @@
         </is>
       </c>
       <c r="Q197" s="2" t="n">
-        <v>134127</v>
+        <v>149321</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>153173</v>
+        <v>151972</v>
       </c>
       <c r="B198" s="2" t="inlineStr"/>
       <c r="C198" s="2" t="inlineStr"/>
-      <c r="D198" s="2" t="inlineStr"/>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>* - Wonder - Maker AR - Looping na atualização da biblioteca</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr"/>
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="2" t="inlineStr">
         <is>
@@ -10572,43 +10568,51 @@
       <c r="H198" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I198" s="2" t="inlineStr"/>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>1963064</t>
+        </is>
+      </c>
       <c r="J198" s="2" t="inlineStr"/>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>Daniel Botogoske</t>
+          <t>Guilherme Fernandes da Silva</t>
         </is>
       </c>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="N198" s="2" t="inlineStr"/>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
-          <t>Promob\Promob Squad</t>
+          <t>Promob\Wonder Squad</t>
         </is>
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2\S13-26 (15-JUN to 26-JUN)</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q198" s="2" t="n">
-        <v>149321</v>
+        <v>134127</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>151972</v>
+        <v>144943</v>
       </c>
       <c r="B199" s="2" t="inlineStr"/>
       <c r="C199" s="2" t="inlineStr"/>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>* - Wonder - Maker AR - Looping na atualização da biblioteca</t>
+          <t>2252149 - Materiais da Greenplac sem veio aplicado</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr"/>
@@ -10623,14 +10627,14 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>1963064</t>
+          <t>2252149</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr"/>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Fernandes da Silva</t>
+          <t>Bruna Scortegagna Rodrigues</t>
         </is>
       </c>
       <c r="M199" s="2" t="inlineStr">
@@ -10640,7 +10644,7 @@
       </c>
       <c r="N199" s="2" t="inlineStr">
         <is>
-          <t>ZendeskTicket</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="O199" s="2" t="inlineStr">
@@ -10650,7 +10654,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob\2026\Q1</t>
         </is>
       </c>
       <c r="Q199" s="2" t="n">
@@ -10659,13 +10663,13 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>144943</v>
+        <v>149721</v>
       </c>
       <c r="B200" s="2" t="inlineStr"/>
       <c r="C200" s="2" t="inlineStr"/>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>2252149 - Materiais da Greenplac sem veio aplicado</t>
+          <t>2256223 - Erro em todos os módulos de RACK da linha Sala</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr"/>
@@ -10680,14 +10684,14 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>2252149</t>
+          <t>2256223</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr"/>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>Bruna Scortegagna Rodrigues</t>
+          <t>Mauricio Barossi</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr">
@@ -10695,11 +10699,7 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N200" s="2" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
+      <c r="N200" s="2" t="inlineStr"/>
       <c r="O200" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q1</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q200" s="2" t="n">
@@ -10716,13 +10716,13 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>149721</v>
+        <v>152080</v>
       </c>
       <c r="B201" s="2" t="inlineStr"/>
       <c r="C201" s="2" t="inlineStr"/>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>2256223 - Erro em todos os módulos de RACK da linha Sala</t>
+          <t>Erro gaveta externa afastamento frontal de gaveta embutida</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr"/>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>2256223</t>
+          <t>1964467</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr"/>
@@ -10752,7 +10752,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N201" s="2" t="inlineStr"/>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.04; ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -10769,13 +10773,13 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>152080</v>
+        <v>142968</v>
       </c>
       <c r="B202" s="2" t="inlineStr"/>
       <c r="C202" s="2" t="inlineStr"/>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Erro gaveta externa afastamento frontal de gaveta embutida</t>
+          <t>AR - Situações Línea Gola</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr"/>
@@ -10788,11 +10792,7 @@
       <c r="H202" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I202" s="2" t="inlineStr">
-        <is>
-          <t>1964467</t>
-        </is>
-      </c>
+      <c r="I202" s="2" t="inlineStr"/>
       <c r="J202" s="2" t="inlineStr"/>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr">
@@ -10805,11 +10805,7 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N202" s="2" t="inlineStr">
-        <is>
-          <t>V.01 R.04; ZendeskTicket</t>
-        </is>
-      </c>
+      <c r="N202" s="2" t="inlineStr"/>
       <c r="O202" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -10817,7 +10813,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob\2026\Q1</t>
         </is>
       </c>
       <c r="Q202" s="2" t="n">
@@ -10826,13 +10822,13 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>142968</v>
+        <v>144948</v>
       </c>
       <c r="B203" s="2" t="inlineStr"/>
       <c r="C203" s="2" t="inlineStr"/>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>AR - Situações Línea Gola</t>
+          <t>2252148 - Prateleira armário alto canto reto de dormitórios</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr"/>
@@ -10845,12 +10841,16 @@
       <c r="H203" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I203" s="2" t="inlineStr"/>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>2252148</t>
+        </is>
+      </c>
       <c r="J203" s="2" t="inlineStr"/>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Barossi</t>
+          <t>Bruna Scortegagna Rodrigues</t>
         </is>
       </c>
       <c r="M203" s="2" t="inlineStr">
@@ -10875,13 +10875,13 @@
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>144948</v>
+        <v>152101</v>
       </c>
       <c r="B204" s="2" t="inlineStr"/>
       <c r="C204" s="2" t="inlineStr"/>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>2252148 - Prateleira armário alto canto reto de dormitórios</t>
+          <t>Furação Maker - Sistema deslizante.</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr"/>
@@ -10896,14 +10896,14 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>2252148</t>
+          <t>1965760</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr"/>
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>Bruna Scortegagna Rodrigues</t>
+          <t>Guilherme Fernandes da Silva</t>
         </is>
       </c>
       <c r="M204" s="2" t="inlineStr">
@@ -10911,7 +10911,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N204" s="2" t="inlineStr"/>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.04; ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -10919,7 +10923,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q1</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q204" s="2" t="n">
@@ -10928,13 +10932,13 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>152101</v>
+        <v>145021</v>
       </c>
       <c r="B205" s="2" t="inlineStr"/>
       <c r="C205" s="2" t="inlineStr"/>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Furação Maker - Sistema deslizante.</t>
+          <t>2252236 - Travessa L não desabilita em Linha Cava</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr"/>
@@ -10949,14 +10953,14 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>1965760</t>
+          <t>2252236</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr"/>
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Fernandes da Silva</t>
+          <t>Bruna Scortegagna Rodrigues</t>
         </is>
       </c>
       <c r="M205" s="2" t="inlineStr">
@@ -10964,11 +10968,7 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N205" s="2" t="inlineStr">
-        <is>
-          <t>V.01 R.04; ZendeskTicket</t>
-        </is>
-      </c>
+      <c r="N205" s="2" t="inlineStr"/>
       <c r="O205" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob\2026\Q1</t>
         </is>
       </c>
       <c r="Q205" s="2" t="n">
@@ -10985,13 +10985,13 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>145021</v>
+        <v>142305</v>
       </c>
       <c r="B206" s="2" t="inlineStr"/>
       <c r="C206" s="2" t="inlineStr"/>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>2252236 - Travessa L não desabilita em Linha Cava</t>
+          <t>2250601 - MAKER AR - Furos para dobradiça Blum não sai na lateral</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr"/>
@@ -11006,14 +11006,14 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>2252236</t>
+          <t>2250601</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr"/>
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>Bruna Scortegagna Rodrigues</t>
+          <t>Jessica Suiani dos Santos Babinski</t>
         </is>
       </c>
       <c r="M206" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q1</t>
+          <t>Promob\2025\Q4</t>
         </is>
       </c>
       <c r="Q206" s="2" t="n">
@@ -11038,13 +11038,13 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>142305</v>
+        <v>136756</v>
       </c>
       <c r="B207" s="2" t="inlineStr"/>
       <c r="C207" s="2" t="inlineStr"/>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>2250601 - MAKER AR - Furos para dobradiça Blum não sai na lateral</t>
+          <t>BR - Ajustar Valor padrão da Descrição do Trilho</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr"/>
@@ -11057,11 +11057,7 @@
       <c r="H207" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I207" s="2" t="inlineStr">
-        <is>
-          <t>2250601</t>
-        </is>
-      </c>
+      <c r="I207" s="2" t="inlineStr"/>
       <c r="J207" s="2" t="inlineStr"/>
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr">
@@ -11082,7 +11078,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>Promob\2025\Q4</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q207" s="2" t="n">
@@ -11091,13 +11087,13 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>136756</v>
+        <v>152215</v>
       </c>
       <c r="B208" s="2" t="inlineStr"/>
       <c r="C208" s="2" t="inlineStr"/>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>BR - Ajustar Valor padrão da Descrição do Trilho</t>
+          <t>** - Wonder - Maker - Configurador de dimensões - Gavetas externas ficando embutidas</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr"/>
@@ -11110,12 +11106,16 @@
       <c r="H208" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I208" s="2" t="inlineStr"/>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>1969153</t>
+        </is>
+      </c>
       <c r="J208" s="2" t="inlineStr"/>
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>Jessica Suiani dos Santos Babinski</t>
+          <t>Mauricio Barossi</t>
         </is>
       </c>
       <c r="M208" s="2" t="inlineStr">
@@ -11123,7 +11123,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N208" s="2" t="inlineStr"/>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.04; ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -11131,7 +11135,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q208" s="2" t="n">
@@ -11140,13 +11144,13 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>152215</v>
+        <v>142934</v>
       </c>
       <c r="B209" s="2" t="inlineStr"/>
       <c r="C209" s="2" t="inlineStr"/>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>** - Wonder - Maker - Configurador de dimensões - Gavetas externas ficando embutidas</t>
+          <t>BR - Porta Basculante Paralela Invisível no ambiente</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr"/>
@@ -11159,16 +11163,12 @@
       <c r="H209" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I209" s="2" t="inlineStr">
-        <is>
-          <t>1969153</t>
-        </is>
-      </c>
+      <c r="I209" s="2" t="inlineStr"/>
       <c r="J209" s="2" t="inlineStr"/>
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Barossi</t>
+          <t>Guilherme Fernandes da Silva</t>
         </is>
       </c>
       <c r="M209" s="2" t="inlineStr">
@@ -11176,11 +11176,7 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N209" s="2" t="inlineStr">
-        <is>
-          <t>V.01 R.04; ZendeskTicket</t>
-        </is>
-      </c>
+      <c r="N209" s="2" t="inlineStr"/>
       <c r="O209" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -11188,7 +11184,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q209" s="2" t="n">
@@ -11197,13 +11193,13 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>142934</v>
+        <v>149730</v>
       </c>
       <c r="B210" s="2" t="inlineStr"/>
       <c r="C210" s="2" t="inlineStr"/>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>BR - Porta Basculante Paralela Invisível no ambiente</t>
+          <t>2256217 - Erro nos módulos Cozinhas Pia</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr"/>
@@ -11216,12 +11212,16 @@
       <c r="H210" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>2256217</t>
+        </is>
+      </c>
       <c r="J210" s="2" t="inlineStr"/>
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Fernandes da Silva</t>
+          <t>Mauricio Barossi</t>
         </is>
       </c>
       <c r="M210" s="2" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q210" s="2" t="n">
@@ -11246,13 +11246,13 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>149730</v>
+        <v>145116</v>
       </c>
       <c r="B211" s="2" t="inlineStr"/>
       <c r="C211" s="2" t="inlineStr"/>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>2256217 - Erro nos módulos Cozinhas Pia</t>
+          <t>2251879 - Base Canto L - Usinagem Corte Errado!</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr"/>
@@ -11267,14 +11267,14 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>2256217</t>
+          <t>2251879</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr"/>
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Barossi</t>
+          <t>Bruna Scortegagna Rodrigues</t>
         </is>
       </c>
       <c r="M211" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob\2026\Q1</t>
         </is>
       </c>
       <c r="Q211" s="2" t="n">
@@ -11299,13 +11299,13 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>145116</v>
+        <v>152585</v>
       </c>
       <c r="B212" s="2" t="inlineStr"/>
       <c r="C212" s="2" t="inlineStr"/>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>2251879 - Base Canto L - Usinagem Corte Errado!</t>
+          <t>1977415 - Wonder Squad - Maker BR - Priorização de furos minifix - Face</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr"/>
@@ -11320,22 +11320,22 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>2251879</t>
+          <t>1977415</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr"/>
       <c r="K212" s="2" t="inlineStr"/>
-      <c r="L212" s="2" t="inlineStr">
-        <is>
-          <t>Bruna Scortegagna Rodrigues</t>
-        </is>
-      </c>
+      <c r="L212" s="2" t="inlineStr"/>
       <c r="M212" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="N212" s="2" t="inlineStr"/>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q1</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q212" s="2" t="n">
@@ -11352,13 +11352,13 @@
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>152585</v>
+        <v>144811</v>
       </c>
       <c r="B213" s="2" t="inlineStr"/>
       <c r="C213" s="2" t="inlineStr"/>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>1977415 - Wonder Squad - Maker BR - Priorização de furos minifix - Face</t>
+          <t>2251326 - Maker AR - Error de perforación en estante movil</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr"/>
@@ -11373,22 +11373,22 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>1977415</t>
+          <t>2251326</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr"/>
       <c r="K213" s="2" t="inlineStr"/>
-      <c r="L213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>Bruna Scortegagna Rodrigues</t>
+        </is>
+      </c>
       <c r="M213" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="N213" s="2" t="inlineStr">
-        <is>
-          <t>ZendeskTicket</t>
-        </is>
-      </c>
+      <c r="N213" s="2" t="inlineStr"/>
       <c r="O213" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob\2026\Q1</t>
         </is>
       </c>
       <c r="Q213" s="2" t="n">
@@ -11405,13 +11405,13 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>144811</v>
+        <v>152980</v>
       </c>
       <c r="B214" s="2" t="inlineStr"/>
       <c r="C214" s="2" t="inlineStr"/>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>2251326 - Maker AR - Error de perforación en estante movil</t>
+          <t>**Wonder - Professional com Cut Pro - Configurador de Dimensões - Gaveta - limita a 500 mm</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr"/>
@@ -11426,14 +11426,14 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>2251326</t>
+          <t>1988880</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr"/>
       <c r="K214" s="2" t="inlineStr"/>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>Bruna Scortegagna Rodrigues</t>
+          <t>Vinicius Consorte Vieira</t>
         </is>
       </c>
       <c r="M214" s="2" t="inlineStr">
@@ -11441,7 +11441,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N214" s="2" t="inlineStr"/>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.04; ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -11449,7 +11453,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q1</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q214" s="2" t="n">
@@ -11458,13 +11462,13 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>152980</v>
+        <v>145723</v>
       </c>
       <c r="B215" s="2" t="inlineStr"/>
       <c r="C215" s="2" t="inlineStr"/>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>**Wonder - Professional com Cut Pro - Configurador de Dimensões - Gaveta - limita a 500 mm</t>
+          <t>**- Wonder - Maker BR - Configuração de fita de borda é aplicada incorretamente nas laterais</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr"/>
@@ -11479,14 +11483,14 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>1988880</t>
+          <t>1714380</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr"/>
       <c r="K215" s="2" t="inlineStr"/>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>Vinicius Consorte Vieira</t>
+          <t>Guilherme Fernandes da Silva</t>
         </is>
       </c>
       <c r="M215" s="2" t="inlineStr">
@@ -11496,7 +11500,7 @@
       </c>
       <c r="N215" s="2" t="inlineStr">
         <is>
-          <t>V.01 R.04; ZendeskTicket</t>
+          <t>ZendeskTicket</t>
         </is>
       </c>
       <c r="O215" s="2" t="inlineStr">
@@ -11506,7 +11510,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob\2026\Q1</t>
         </is>
       </c>
       <c r="Q215" s="2" t="n">
@@ -11515,13 +11519,13 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>145723</v>
+        <v>150872</v>
       </c>
       <c r="B216" s="2" t="inlineStr"/>
       <c r="C216" s="2" t="inlineStr"/>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>**- Wonder - Maker BR - Configuração de fita de borda é aplicada incorretamente nas laterais</t>
+          <t>** - Wonder - Maker Br - Conf Biblioteca Form - Modulo pia desconfigura ao alterar altura</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr"/>
@@ -11536,14 +11540,14 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>1714380</t>
+          <t>1929843</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr"/>
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Fernandes da Silva</t>
+          <t>Mauricio Barossi</t>
         </is>
       </c>
       <c r="M216" s="2" t="inlineStr">
@@ -11563,7 +11567,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q1</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q216" s="2" t="n">
@@ -11572,13 +11576,13 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>150872</v>
+        <v>153018</v>
       </c>
       <c r="B217" s="2" t="inlineStr"/>
       <c r="C217" s="2" t="inlineStr"/>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>** - Wonder - Maker Br - Conf Biblioteca Form - Modulo pia desconfigura ao alterar altura</t>
+          <t>** - Wonder - Maker Br - Configurador de Dimensões - Fita de Borda não é aplicada na lateral</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr"/>
@@ -11593,14 +11597,14 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>1929843</t>
+          <t>1990232</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr"/>
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Barossi</t>
+          <t>Guilherme Fernandes da Silva</t>
         </is>
       </c>
       <c r="M217" s="2" t="inlineStr">
@@ -11629,13 +11633,13 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>153018</v>
+        <v>145730</v>
       </c>
       <c r="B218" s="2" t="inlineStr"/>
       <c r="C218" s="2" t="inlineStr"/>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>** - Wonder - Maker Br - Configurador de Dimensões - Fita de Borda não é aplicada na lateral</t>
+          <t>2252842 - Porta basculante sem Cava na Linha Cava Madeira</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr"/>
@@ -11650,14 +11654,14 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>1990232</t>
+          <t xml:space="preserve">2252842 </t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr"/>
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Fernandes da Silva</t>
+          <t>Bruna Scortegagna Rodrigues</t>
         </is>
       </c>
       <c r="M218" s="2" t="inlineStr">
@@ -11665,11 +11669,7 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N218" s="2" t="inlineStr">
-        <is>
-          <t>ZendeskTicket</t>
-        </is>
-      </c>
+      <c r="N218" s="2" t="inlineStr"/>
       <c r="O218" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob\2026\Q1</t>
         </is>
       </c>
       <c r="Q218" s="2" t="n">
@@ -11686,13 +11686,13 @@
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>145730</v>
+        <v>148776</v>
       </c>
       <c r="B219" s="2" t="inlineStr"/>
       <c r="C219" s="2" t="inlineStr"/>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>2252842 - Porta basculante sem Cava na Linha Cava Madeira</t>
+          <t>* - Wonder - Maker BR - Modulações | Cozinha Cava - Largura mínima menor que 300</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr"/>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2252842 </t>
+          <t>1870918</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr"/>
@@ -11722,7 +11722,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N219" s="2" t="inlineStr"/>
+      <c r="N219" s="2" t="inlineStr">
+        <is>
+          <t>ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -11730,7 +11734,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q1</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q219" s="2" t="n">
@@ -11739,13 +11743,13 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>148776</v>
+        <v>153402</v>
       </c>
       <c r="B220" s="2" t="inlineStr"/>
       <c r="C220" s="2" t="inlineStr"/>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>* - Wonder - Maker BR - Modulações | Cozinha Cava - Largura mínima menor que 300</t>
+          <t>** - Wonder - Maber Br - Modulação - Cantoneira Cozinha não redimensiona ao diminuir tamanho</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr"/>
@@ -11760,14 +11764,14 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>1870918</t>
+          <t>1999636</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr"/>
       <c r="K220" s="2" t="inlineStr"/>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>Bruna Scortegagna Rodrigues</t>
+          <t>Mauricio Barossi</t>
         </is>
       </c>
       <c r="M220" s="2" t="inlineStr">
@@ -11777,7 +11781,7 @@
       </c>
       <c r="N220" s="2" t="inlineStr">
         <is>
-          <t>ZendeskTicket</t>
+          <t>V.01 R.04; ZendeskTicket</t>
         </is>
       </c>
       <c r="O220" s="2" t="inlineStr">
@@ -11796,13 +11800,13 @@
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>153402</v>
+        <v>136876</v>
       </c>
       <c r="B221" s="2" t="inlineStr"/>
       <c r="C221" s="2" t="inlineStr"/>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>** - Wonder - Maber Br - Modulação - Cantoneira Cozinha não redimensiona ao diminuir tamanho</t>
+          <t>BR - Peças de Gavetas com Posicionamento Incorreto</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr"/>
@@ -11815,16 +11819,12 @@
       <c r="H221" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I221" s="2" t="inlineStr">
-        <is>
-          <t>1999636</t>
-        </is>
-      </c>
+      <c r="I221" s="2" t="inlineStr"/>
       <c r="J221" s="2" t="inlineStr"/>
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Barossi</t>
+          <t>Jessica Suiani dos Santos Babinski</t>
         </is>
       </c>
       <c r="M221" s="2" t="inlineStr">
@@ -11832,11 +11832,7 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N221" s="2" t="inlineStr">
-        <is>
-          <t>V.01 R.04; ZendeskTicket</t>
-        </is>
-      </c>
+      <c r="N221" s="2" t="inlineStr"/>
       <c r="O221" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -11844,7 +11840,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob</t>
         </is>
       </c>
       <c r="Q221" s="2" t="n">
@@ -11853,13 +11849,13 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>136876</v>
+        <v>134203</v>
       </c>
       <c r="B222" s="2" t="inlineStr"/>
       <c r="C222" s="2" t="inlineStr"/>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>BR - Peças de Gavetas com Posicionamento Incorreto</t>
+          <t>2241915 - Prateleiras de módulos colunas redimensionando errado</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr"/>
@@ -11870,14 +11866,18 @@
         </is>
       </c>
       <c r="H222" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I222" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2241915 </t>
+        </is>
+      </c>
       <c r="J222" s="2" t="inlineStr"/>
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>Jessica Suiani dos Santos Babinski</t>
+          <t>Gustavo Garbin de Lima</t>
         </is>
       </c>
       <c r="M222" s="2" t="inlineStr">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>Promob</t>
+          <t>Promob\2025\Q3</t>
         </is>
       </c>
       <c r="Q222" s="2" t="n">
@@ -11902,13 +11902,13 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>134203</v>
+        <v>139311</v>
       </c>
       <c r="B223" s="2" t="inlineStr"/>
       <c r="C223" s="2" t="inlineStr"/>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>2241915 - Prateleiras de módulos colunas redimensionando errado</t>
+          <t>2247782 - Promob Maker BR - Configuração de Dimensões | Cava Central - Não altera as dimensões aplicadas</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr"/>
@@ -11919,11 +11919,11 @@
         </is>
       </c>
       <c r="H223" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241915 </t>
+          <t>2247782</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr"/>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>Promob\2025\Q3</t>
+          <t>Promob\2025\Q4</t>
         </is>
       </c>
       <c r="Q223" s="2" t="n">
@@ -11955,13 +11955,13 @@
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>139311</v>
+        <v>139833</v>
       </c>
       <c r="B224" s="2" t="inlineStr"/>
       <c r="C224" s="2" t="inlineStr"/>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>2247782 - Promob Maker BR - Configuração de Dimensões | Cava Central - Não altera as dimensões aplicadas</t>
+          <t>2248061 - Promob Plus 5.60.41.3 - Modelos - Material Palha - Qualidade ao renderizar e aplicar</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr"/>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>2247782</t>
+          <t xml:space="preserve">2248061 </t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr"/>
@@ -12008,13 +12008,13 @@
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>139833</v>
+        <v>149723</v>
       </c>
       <c r="B225" s="2" t="inlineStr"/>
       <c r="C225" s="2" t="inlineStr"/>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>2248061 - Promob Plus 5.60.41.3 - Modelos - Material Palha - Qualidade ao renderizar e aplicar</t>
+          <t>2256221 - Erro nos armários inferiores de sala</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr"/>
@@ -12029,14 +12029,14 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2248061 </t>
+          <t>2256221</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr"/>
       <c r="K225" s="2" t="inlineStr"/>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Garbin de Lima</t>
+          <t>Jessica Suiani dos Santos Babinski</t>
         </is>
       </c>
       <c r="M225" s="2" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>Promob\2025\Q4</t>
+          <t>Promob\2026\Q2</t>
         </is>
       </c>
       <c r="Q225" s="2" t="n">
@@ -12061,13 +12061,13 @@
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>149723</v>
+        <v>150435</v>
       </c>
       <c r="B226" s="2" t="inlineStr"/>
       <c r="C226" s="2" t="inlineStr"/>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>2256221 - Erro nos armários inferiores de sala</t>
+          <t>2256901 - Processo usinagem kit desempenador para Embutir</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr"/>
@@ -12082,14 +12082,14 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>2256221</t>
+          <t>2256901</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr"/>
       <c r="K226" s="2" t="inlineStr"/>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>Jessica Suiani dos Santos Babinski</t>
+          <t>Mauricio Barossi</t>
         </is>
       </c>
       <c r="M226" s="2" t="inlineStr">
@@ -12114,13 +12114,13 @@
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>150435</v>
+        <v>151110</v>
       </c>
       <c r="B227" s="2" t="inlineStr"/>
       <c r="C227" s="2" t="inlineStr"/>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>2256901 - Processo usinagem kit desempenador para Embutir</t>
+          <t>Promob Maker BR - Update - Looping de atualização System</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr"/>
@@ -12135,14 +12135,14 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>2256901</t>
+          <t>1938187</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr"/>
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Barossi</t>
+          <t>Gustavo Garbin de Lima</t>
         </is>
       </c>
       <c r="M227" s="2" t="inlineStr">
@@ -12150,7 +12150,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N227" s="2" t="inlineStr"/>
+      <c r="N227" s="2" t="inlineStr">
+        <is>
+          <t>ZendeskTicket</t>
+        </is>
+      </c>
       <c r="O227" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -12167,13 +12171,13 @@
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>151110</v>
+        <v>151169</v>
       </c>
       <c r="B228" s="2" t="inlineStr"/>
       <c r="C228" s="2" t="inlineStr"/>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Promob Maker BR - Update - Looping de atualização System</t>
+          <t>* - Wonder Squad - Plus - Looping na atualização</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr"/>
@@ -12188,7 +12192,7 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>1938187</t>
+          <t>1939732</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr"/>
@@ -12224,13 +12228,13 @@
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>151169</v>
+        <v>151198</v>
       </c>
       <c r="B229" s="2" t="inlineStr"/>
       <c r="C229" s="2" t="inlineStr"/>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>* - Wonder Squad - Plus - Looping na atualização</t>
+          <t>* - Wonder Squad - Plus - Material pérola urbana fica cinza</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr"/>
@@ -12245,14 +12249,14 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>1939732</t>
+          <t>1941308</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr"/>
       <c r="K229" s="2" t="inlineStr"/>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Garbin de Lima</t>
+          <t>Guilherme Fernandes da Silva</t>
         </is>
       </c>
       <c r="M229" s="2" t="inlineStr">
@@ -12262,7 +12266,7 @@
       </c>
       <c r="N229" s="2" t="inlineStr">
         <is>
-          <t>ZendeskTicket</t>
+          <t>NI; ZendeskTicket</t>
         </is>
       </c>
       <c r="O229" s="2" t="inlineStr">
@@ -12281,13 +12285,13 @@
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>151198</v>
+        <v>151707</v>
       </c>
       <c r="B230" s="2" t="inlineStr"/>
       <c r="C230" s="2" t="inlineStr"/>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>* - Wonder Squad - Plus - Material pérola urbana fica cinza</t>
+          <t xml:space="preserve">** - Wonder - Plus Professional/Enterprise - Modelos - Duratex - Modelos são apresentados brancos </t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr"/>
@@ -12302,7 +12306,7 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>1941308</t>
+          <t>1956155</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr"/>
@@ -12324,7 +12328,7 @@
       </c>
       <c r="O230" s="2" t="inlineStr">
         <is>
-          <t>Promob\Wonder Squad</t>
+          <t>Promob\Wonder Squad\Plus</t>
         </is>
       </c>
       <c r="P230" s="2" t="inlineStr">
@@ -12338,13 +12342,13 @@
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>151707</v>
+        <v>156958</v>
       </c>
       <c r="B231" s="2" t="inlineStr"/>
       <c r="C231" s="2" t="inlineStr"/>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">** - Wonder - Plus Professional/Enterprise - Modelos - Duratex - Modelos são apresentados brancos </t>
+          <t>** - Wonder - Plus - Modelo - Porta Colonial - Modelo fica desconfigurado</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr"/>
@@ -12355,18 +12359,18 @@
         </is>
       </c>
       <c r="H231" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>1956155</t>
+          <t>2083127</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr"/>
       <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Fernandes da Silva</t>
+          <t>Heloisa Schweizer de Oliveira</t>
         </is>
       </c>
       <c r="M231" s="2" t="inlineStr">
@@ -12376,17 +12380,17 @@
       </c>
       <c r="N231" s="2" t="inlineStr">
         <is>
-          <t>NI; ZendeskTicket</t>
+          <t>ZendeskTicket</t>
         </is>
       </c>
       <c r="O231" s="2" t="inlineStr">
         <is>
-          <t>Promob\Wonder Squad\Plus</t>
+          <t>Promob\Wonder Squad</t>
         </is>
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>Promob\2026\Q2</t>
+          <t>Promob\2026\Q3</t>
         </is>
       </c>
       <c r="Q231" s="2" t="n">
@@ -19758,7 +19762,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N371" s="2" t="inlineStr"/>
+      <c r="N371" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O371" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -19803,7 +19811,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N372" s="2" t="inlineStr"/>
+      <c r="N372" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O372" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -19848,7 +19860,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N373" s="2" t="inlineStr"/>
+      <c r="N373" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O373" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -19897,7 +19913,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N374" s="2" t="inlineStr"/>
+      <c r="N374" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O374" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -19946,7 +19966,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N375" s="2" t="inlineStr"/>
+      <c r="N375" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O375" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -19995,7 +20019,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N376" s="2" t="inlineStr"/>
+      <c r="N376" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O376" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20044,7 +20072,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N377" s="2" t="inlineStr"/>
+      <c r="N377" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O377" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20093,7 +20125,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N378" s="2" t="inlineStr"/>
+      <c r="N378" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O378" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20142,7 +20178,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N379" s="2" t="inlineStr"/>
+      <c r="N379" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O379" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20191,7 +20231,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N380" s="2" t="inlineStr"/>
+      <c r="N380" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O380" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20240,7 +20284,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N381" s="2" t="inlineStr"/>
+      <c r="N381" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O381" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20289,7 +20337,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N382" s="2" t="inlineStr"/>
+      <c r="N382" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O382" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20338,7 +20390,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N383" s="2" t="inlineStr"/>
+      <c r="N383" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O383" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20387,7 +20443,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N384" s="2" t="inlineStr"/>
+      <c r="N384" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O384" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20436,7 +20496,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N385" s="2" t="inlineStr"/>
+      <c r="N385" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O385" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20485,7 +20549,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N386" s="2" t="inlineStr"/>
+      <c r="N386" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O386" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20534,7 +20602,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N387" s="2" t="inlineStr"/>
+      <c r="N387" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O387" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20583,7 +20655,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N388" s="2" t="inlineStr"/>
+      <c r="N388" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O388" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20619,7 +20695,11 @@
       <c r="H389" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I389" s="2" t="inlineStr"/>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>2262130</t>
+        </is>
+      </c>
       <c r="J389" s="2" t="inlineStr"/>
       <c r="K389" s="2" t="inlineStr"/>
       <c r="L389" s="2" t="inlineStr"/>
@@ -20628,7 +20708,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N389" s="2" t="inlineStr"/>
+      <c r="N389" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O389" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20664,7 +20748,11 @@
       <c r="H390" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I390" s="2" t="inlineStr"/>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>2263735</t>
+        </is>
+      </c>
       <c r="J390" s="2" t="inlineStr"/>
       <c r="K390" s="2" t="inlineStr"/>
       <c r="L390" s="2" t="inlineStr"/>
@@ -20673,7 +20761,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N390" s="2" t="inlineStr"/>
+      <c r="N390" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O390" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20709,7 +20801,11 @@
       <c r="H391" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I391" s="2" t="inlineStr"/>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>2263736</t>
+        </is>
+      </c>
       <c r="J391" s="2" t="inlineStr"/>
       <c r="K391" s="2" t="inlineStr"/>
       <c r="L391" s="2" t="inlineStr"/>
@@ -20718,7 +20814,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N391" s="2" t="inlineStr"/>
+      <c r="N391" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O391" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20754,7 +20854,11 @@
       <c r="H392" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I392" s="2" t="inlineStr"/>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>2248677</t>
+        </is>
+      </c>
       <c r="J392" s="2" t="inlineStr"/>
       <c r="K392" s="2" t="inlineStr"/>
       <c r="L392" s="2" t="inlineStr"/>
@@ -20763,7 +20867,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N392" s="2" t="inlineStr"/>
+      <c r="N392" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O392" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20799,7 +20907,11 @@
       <c r="H393" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I393" s="2" t="inlineStr"/>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>2260730</t>
+        </is>
+      </c>
       <c r="J393" s="2" t="inlineStr"/>
       <c r="K393" s="2" t="inlineStr"/>
       <c r="L393" s="2" t="inlineStr"/>
@@ -20808,7 +20920,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N393" s="2" t="inlineStr"/>
+      <c r="N393" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O393" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20857,7 +20973,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N394" s="2" t="inlineStr"/>
+      <c r="N394" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O394" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20893,7 +21013,11 @@
       <c r="H395" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I395" s="2" t="inlineStr"/>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t>2262472</t>
+        </is>
+      </c>
       <c r="J395" s="2" t="inlineStr"/>
       <c r="K395" s="2" t="inlineStr"/>
       <c r="L395" s="2" t="inlineStr"/>
@@ -20902,7 +21026,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N395" s="2" t="inlineStr"/>
+      <c r="N395" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O395" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -20919,13 +21047,13 @@
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>160322</v>
+        <v>160385</v>
       </c>
       <c r="B396" s="2" t="inlineStr"/>
       <c r="C396" s="2" t="inlineStr"/>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>2262472 - Itens Aguardando Liberação_Grupo Avant Box Slowmotion</t>
+          <t>2263945 - Acabamentos indisponíveis</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr"/>
@@ -20938,7 +21066,11 @@
       <c r="H396" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I396" s="2" t="inlineStr"/>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>2263945</t>
+        </is>
+      </c>
       <c r="J396" s="2" t="inlineStr"/>
       <c r="K396" s="2" t="inlineStr"/>
       <c r="L396" s="2" t="inlineStr"/>
@@ -20947,7 +21079,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N396" s="2" t="inlineStr"/>
+      <c r="N396" s="2" t="inlineStr">
+        <is>
+          <t>e-desk</t>
+        </is>
+      </c>
       <c r="O396" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -32073,7 +32209,7 @@
       <c r="F611" s="2" t="inlineStr"/>
       <c r="G611" s="2" t="inlineStr">
         <is>
-          <t>QA Pile</t>
+          <t>Validating</t>
         </is>
       </c>
       <c r="H611" s="2" t="n">
@@ -34110,7 +34246,7 @@
       <c r="F650" s="2" t="inlineStr"/>
       <c r="G650" s="2" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H650" s="2" t="n">
@@ -34790,7 +34926,7 @@
       <c r="F664" s="2" t="inlineStr"/>
       <c r="G664" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>QA Pile</t>
         </is>
       </c>
       <c r="H664" s="2" t="n">
@@ -34845,7 +34981,7 @@
       </c>
       <c r="G665" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H665" s="2" t="n">

--- a/LISTA.xlsx
+++ b/LISTA.xlsx
@@ -1558,7 +1558,7 @@
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>QA Pile</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
@@ -1892,7 +1892,7 @@
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
@@ -1905,7 +1905,11 @@
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Mauricio Barossi</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -2043,7 +2047,7 @@
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
@@ -2210,7 +2214,7 @@
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>QA Pile</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
@@ -2703,7 +2707,7 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
@@ -2728,7 +2732,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>ZendeskTicket</t>
+          <t>V.01 R.05; V.13 R.35; ZendeskTicket</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -2817,7 +2821,7 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
@@ -2842,7 +2846,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>ZendeskTicket</t>
+          <t>V.01 R.05; V.13 R.35; ZendeskTicket</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3738,7 +3742,7 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
@@ -3751,7 +3755,11 @@
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Guilherme Lamb De Souza</t>
+        </is>
+      </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -4126,7 +4134,7 @@
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
@@ -4149,7 +4157,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="N70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>V.01 R.05; V.13 R.35</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
           <t>Promob\Wonder Squad</t>
@@ -4505,7 +4517,7 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Validating</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
@@ -4562,7 +4574,7 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H78" s="2" t="n">
@@ -4588,7 +4600,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Promob\Wonder Squad</t>
+          <t>Promob\Promob Squad</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -20851,7 +20863,7 @@
       <c r="F391" s="2" t="inlineStr"/>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H391" s="2" t="n">
@@ -20864,7 +20876,11 @@
       </c>
       <c r="J391" s="2" t="inlineStr"/>
       <c r="K391" s="2" t="inlineStr"/>
-      <c r="L391" s="2" t="inlineStr"/>
+      <c r="L391" s="2" t="inlineStr">
+        <is>
+          <t>Guilherme Lamb De Souza</t>
+        </is>
+      </c>
       <c r="M391" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -20872,7 +20888,7 @@
       </c>
       <c r="N391" s="2" t="inlineStr">
         <is>
-          <t>e-desk</t>
+          <t>e-desk; V.01 R.05</t>
         </is>
       </c>
       <c r="O391" s="2" t="inlineStr">
@@ -21014,7 +21030,7 @@
       <c r="F394" s="2" t="inlineStr"/>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H394" s="2" t="n">
@@ -21027,7 +21043,11 @@
       </c>
       <c r="J394" s="2" t="inlineStr"/>
       <c r="K394" s="2" t="inlineStr"/>
-      <c r="L394" s="2" t="inlineStr"/>
+      <c r="L394" s="2" t="inlineStr">
+        <is>
+          <t>Guilherme Lamb De Souza</t>
+        </is>
+      </c>
       <c r="M394" s="2" t="inlineStr">
         <is>
           <t>Bug</t>
@@ -21035,7 +21055,7 @@
       </c>
       <c r="N394" s="2" t="inlineStr">
         <is>
-          <t>e-desk</t>
+          <t>e-desk; V.01 R.05</t>
         </is>
       </c>
       <c r="O394" s="2" t="inlineStr">
@@ -32742,7 +32762,7 @@
       <c r="F620" s="2" t="inlineStr"/>
       <c r="G620" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Paused</t>
         </is>
       </c>
       <c r="H620" s="2" t="n">
